--- a/docs/CodeSignal/record.xlsx
+++ b/docs/CodeSignal/record.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\everyday-use\Blog\docs\CodeSignal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8B44C11-83D5-406B-AC54-8C62D1790C2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BB868B0-9B15-4DE4-86C6-BA58AF556285}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19020" yWindow="0" windowWidth="19380" windowHeight="20970" tabRatio="511" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" tabRatio="511" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CodeSignalの記録" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2072" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2076" uniqueCount="120">
   <si>
     <t>番号</t>
   </si>
@@ -947,7 +947,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:L516"/>
+  <dimension ref="A1:L517"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="7.7265625" style="10" bestFit="1" customWidth="1"/>
@@ -13446,7 +13446,7 @@
     </row>
     <row r="315" spans="1:12" ht="24" customHeight="1">
       <c r="A315" s="5">
-        <f t="shared" ref="A315:A516" si="8">ROW()-1</f>
+        <f t="shared" ref="A315:A517" si="8">ROW()-1</f>
         <v>314</v>
       </c>
       <c r="B315" s="6">
@@ -19330,7 +19330,7 @@
         <v>461</v>
       </c>
       <c r="B462" s="6">
-        <f t="shared" ref="B462:B516" si="10">B461+1</f>
+        <f t="shared" ref="B462:B517" si="10">B461+1</f>
         <v>46223</v>
       </c>
       <c r="C462" s="5">
@@ -21521,6 +21521,46 @@
         <v>1</v>
       </c>
       <c r="L516" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="517" spans="1:12" ht="24" customHeight="1">
+      <c r="A517" s="5">
+        <f t="shared" si="8"/>
+        <v>516</v>
+      </c>
+      <c r="B517" s="6">
+        <f t="shared" si="10"/>
+        <v>46278</v>
+      </c>
+      <c r="C517" s="5">
+        <v>813</v>
+      </c>
+      <c r="D517" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="E517" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="F517" s="5">
+        <v>4</v>
+      </c>
+      <c r="G517" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="H517" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="I517" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="J517" s="5">
+        <v>1</v>
+      </c>
+      <c r="K517" s="5">
+        <v>1</v>
+      </c>
+      <c r="L517" s="5">
         <v>1</v>
       </c>
     </row>
@@ -22509,8 +22549,10 @@
     <hyperlink ref="H515" r:id="rId979" xr:uid="{69919DBD-6AD1-45A5-81A7-DA983297FFBA}"/>
     <hyperlink ref="E516" r:id="rId980" xr:uid="{FB8CF722-33A2-4B4E-AA09-171EF1E4564F}"/>
     <hyperlink ref="H516" r:id="rId981" xr:uid="{9A89EDCD-C0FE-4207-9F17-31FE155BCCE9}"/>
+    <hyperlink ref="E517" r:id="rId982" xr:uid="{EE3E0E3D-5CDF-4CD9-854B-E0D982B327E4}"/>
+    <hyperlink ref="H517" r:id="rId983" xr:uid="{FA98B9D6-8418-4D00-A844-EDAC331B9A8E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId982"/>
+  <pageSetup orientation="portrait" r:id="rId984"/>
 </worksheet>
 </file>
--- a/docs/CodeSignal/record.xlsx
+++ b/docs/CodeSignal/record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\everyday-use\Blog\docs\CodeSignal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BB868B0-9B15-4DE4-86C6-BA58AF556285}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC43A946-A389-4402-A239-B130E2B31E99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" tabRatio="511" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2076" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2080" uniqueCount="120">
   <si>
     <t>番号</t>
   </si>
@@ -947,7 +947,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:L517"/>
+  <dimension ref="A1:L518"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="7.7265625" style="10" bestFit="1" customWidth="1"/>
@@ -13446,7 +13446,7 @@
     </row>
     <row r="315" spans="1:12" ht="24" customHeight="1">
       <c r="A315" s="5">
-        <f t="shared" ref="A315:A517" si="8">ROW()-1</f>
+        <f t="shared" ref="A315:A518" si="8">ROW()-1</f>
         <v>314</v>
       </c>
       <c r="B315" s="6">
@@ -19330,7 +19330,7 @@
         <v>461</v>
       </c>
       <c r="B462" s="6">
-        <f t="shared" ref="B462:B517" si="10">B461+1</f>
+        <f t="shared" ref="B462:B518" si="10">B461+1</f>
         <v>46223</v>
       </c>
       <c r="C462" s="5">
@@ -21562,6 +21562,46 @@
       </c>
       <c r="L517" s="5">
         <v>1</v>
+      </c>
+    </row>
+    <row r="518" spans="1:12" ht="24" customHeight="1">
+      <c r="A518" s="5">
+        <f t="shared" si="8"/>
+        <v>517</v>
+      </c>
+      <c r="B518" s="6">
+        <f t="shared" si="10"/>
+        <v>46279</v>
+      </c>
+      <c r="C518" s="5">
+        <v>814</v>
+      </c>
+      <c r="D518" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="E518" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="F518" s="5">
+        <v>4</v>
+      </c>
+      <c r="G518" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="H518" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="I518" s="9">
+        <v>0.23</v>
+      </c>
+      <c r="J518" s="5">
+        <v>2</v>
+      </c>
+      <c r="K518" s="5">
+        <v>0</v>
+      </c>
+      <c r="L518" s="5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -22551,8 +22591,10 @@
     <hyperlink ref="H516" r:id="rId981" xr:uid="{9A89EDCD-C0FE-4207-9F17-31FE155BCCE9}"/>
     <hyperlink ref="E517" r:id="rId982" xr:uid="{EE3E0E3D-5CDF-4CD9-854B-E0D982B327E4}"/>
     <hyperlink ref="H517" r:id="rId983" xr:uid="{FA98B9D6-8418-4D00-A844-EDAC331B9A8E}"/>
+    <hyperlink ref="E518" r:id="rId984" xr:uid="{FD2DC81E-3BF0-4DDD-BF08-A6B6599A5AEC}"/>
+    <hyperlink ref="H518" r:id="rId985" xr:uid="{A0A75938-FD9C-4AFC-9954-2BF742C34D88}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId984"/>
+  <pageSetup orientation="portrait" r:id="rId986"/>
 </worksheet>
 </file>
--- a/docs/CodeSignal/record.xlsx
+++ b/docs/CodeSignal/record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\everyday-use\Blog\docs\CodeSignal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC43A946-A389-4402-A239-B130E2B31E99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB747090-47AA-4739-ADAC-194D5ECA4D9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" tabRatio="511" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2080" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2084" uniqueCount="120">
   <si>
     <t>番号</t>
   </si>
@@ -947,7 +947,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:L518"/>
+  <dimension ref="A1:L519"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="7.7265625" style="10" bestFit="1" customWidth="1"/>
@@ -13446,7 +13446,7 @@
     </row>
     <row r="315" spans="1:12" ht="24" customHeight="1">
       <c r="A315" s="5">
-        <f t="shared" ref="A315:A518" si="8">ROW()-1</f>
+        <f t="shared" ref="A315:A519" si="8">ROW()-1</f>
         <v>314</v>
       </c>
       <c r="B315" s="6">
@@ -19330,7 +19330,7 @@
         <v>461</v>
       </c>
       <c r="B462" s="6">
-        <f t="shared" ref="B462:B518" si="10">B461+1</f>
+        <f t="shared" ref="B462:B519" si="10">B461+1</f>
         <v>46223</v>
       </c>
       <c r="C462" s="5">
@@ -21602,6 +21602,46 @@
       </c>
       <c r="L518" s="5">
         <v>0</v>
+      </c>
+    </row>
+    <row r="519" spans="1:12" ht="24" customHeight="1">
+      <c r="A519" s="5">
+        <f t="shared" si="8"/>
+        <v>518</v>
+      </c>
+      <c r="B519" s="6">
+        <f t="shared" si="10"/>
+        <v>46280</v>
+      </c>
+      <c r="C519" s="5">
+        <v>815</v>
+      </c>
+      <c r="D519" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="E519" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="F519" s="5">
+        <v>4</v>
+      </c>
+      <c r="G519" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="H519" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="I519" s="9">
+        <v>0.27</v>
+      </c>
+      <c r="J519" s="5">
+        <v>2</v>
+      </c>
+      <c r="K519" s="5">
+        <v>1</v>
+      </c>
+      <c r="L519" s="5">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -22593,8 +22633,10 @@
     <hyperlink ref="H517" r:id="rId983" xr:uid="{FA98B9D6-8418-4D00-A844-EDAC331B9A8E}"/>
     <hyperlink ref="E518" r:id="rId984" xr:uid="{FD2DC81E-3BF0-4DDD-BF08-A6B6599A5AEC}"/>
     <hyperlink ref="H518" r:id="rId985" xr:uid="{A0A75938-FD9C-4AFC-9954-2BF742C34D88}"/>
+    <hyperlink ref="E519" r:id="rId986" xr:uid="{1FA272D3-363E-44DC-8679-E57C06AD8586}"/>
+    <hyperlink ref="H519" r:id="rId987" xr:uid="{F8A797C3-2C08-44C6-9C4B-3E67DCA94155}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId986"/>
+  <pageSetup orientation="portrait" r:id="rId988"/>
 </worksheet>
 </file>
--- a/docs/CodeSignal/record.xlsx
+++ b/docs/CodeSignal/record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\everyday-use\Blog\docs\CodeSignal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB747090-47AA-4739-ADAC-194D5ECA4D9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66B2E796-C40C-40DB-841B-33C79DC0049C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" tabRatio="511" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2084" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2088" uniqueCount="120">
   <si>
     <t>番号</t>
   </si>
@@ -947,7 +947,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:L519"/>
+  <dimension ref="A1:L520"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="7.7265625" style="10" bestFit="1" customWidth="1"/>
@@ -13446,7 +13446,7 @@
     </row>
     <row r="315" spans="1:12" ht="24" customHeight="1">
       <c r="A315" s="5">
-        <f t="shared" ref="A315:A519" si="8">ROW()-1</f>
+        <f t="shared" ref="A315:A520" si="8">ROW()-1</f>
         <v>314</v>
       </c>
       <c r="B315" s="6">
@@ -19330,7 +19330,7 @@
         <v>461</v>
       </c>
       <c r="B462" s="6">
-        <f t="shared" ref="B462:B519" si="10">B461+1</f>
+        <f t="shared" ref="B462:B520" si="10">B461+1</f>
         <v>46223</v>
       </c>
       <c r="C462" s="5">
@@ -21641,6 +21641,46 @@
         <v>1</v>
       </c>
       <c r="L519" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="520" spans="1:12" ht="24" customHeight="1">
+      <c r="A520" s="5">
+        <f t="shared" si="8"/>
+        <v>519</v>
+      </c>
+      <c r="B520" s="6">
+        <f t="shared" si="10"/>
+        <v>46281</v>
+      </c>
+      <c r="C520" s="5">
+        <v>816</v>
+      </c>
+      <c r="D520" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="E520" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="F520" s="5">
+        <v>4</v>
+      </c>
+      <c r="G520" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="H520" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="I520" s="9">
+        <v>0.3</v>
+      </c>
+      <c r="J520" s="5">
+        <v>2</v>
+      </c>
+      <c r="K520" s="5">
+        <v>1</v>
+      </c>
+      <c r="L520" s="5">
         <v>1</v>
       </c>
     </row>
@@ -22635,8 +22675,10 @@
     <hyperlink ref="H518" r:id="rId985" xr:uid="{A0A75938-FD9C-4AFC-9954-2BF742C34D88}"/>
     <hyperlink ref="E519" r:id="rId986" xr:uid="{1FA272D3-363E-44DC-8679-E57C06AD8586}"/>
     <hyperlink ref="H519" r:id="rId987" xr:uid="{F8A797C3-2C08-44C6-9C4B-3E67DCA94155}"/>
+    <hyperlink ref="E520" r:id="rId988" xr:uid="{43570C22-BEB1-4F31-91A8-E6109AE9A2BC}"/>
+    <hyperlink ref="H520" r:id="rId989" xr:uid="{A5D96057-849F-42B3-9419-CA8A37EF8E5B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId988"/>
+  <pageSetup orientation="portrait" r:id="rId990"/>
 </worksheet>
 </file>
--- a/docs/CodeSignal/record.xlsx
+++ b/docs/CodeSignal/record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\everyday-use\Blog\docs\CodeSignal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66B2E796-C40C-40DB-841B-33C79DC0049C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{174BA40E-8B66-413E-909E-F81677E5F6A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" tabRatio="511" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2088" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2092" uniqueCount="120">
   <si>
     <t>番号</t>
   </si>
@@ -947,7 +947,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:L520"/>
+  <dimension ref="A1:L521"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="7.7265625" style="10" bestFit="1" customWidth="1"/>
@@ -13446,7 +13446,7 @@
     </row>
     <row r="315" spans="1:12" ht="24" customHeight="1">
       <c r="A315" s="5">
-        <f t="shared" ref="A315:A520" si="8">ROW()-1</f>
+        <f t="shared" ref="A315:A521" si="8">ROW()-1</f>
         <v>314</v>
       </c>
       <c r="B315" s="6">
@@ -19330,7 +19330,7 @@
         <v>461</v>
       </c>
       <c r="B462" s="6">
-        <f t="shared" ref="B462:B520" si="10">B461+1</f>
+        <f t="shared" ref="B462:B521" si="10">B461+1</f>
         <v>46223</v>
       </c>
       <c r="C462" s="5">
@@ -21681,6 +21681,46 @@
         <v>1</v>
       </c>
       <c r="L520" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="521" spans="1:12" ht="24" customHeight="1">
+      <c r="A521" s="5">
+        <f t="shared" si="8"/>
+        <v>520</v>
+      </c>
+      <c r="B521" s="6">
+        <f t="shared" si="10"/>
+        <v>46282</v>
+      </c>
+      <c r="C521" s="5">
+        <v>816</v>
+      </c>
+      <c r="D521" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="E521" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="F521" s="5">
+        <v>4</v>
+      </c>
+      <c r="G521" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="H521" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="I521" s="9">
+        <v>0.33</v>
+      </c>
+      <c r="J521" s="5">
+        <v>2</v>
+      </c>
+      <c r="K521" s="5">
+        <v>1</v>
+      </c>
+      <c r="L521" s="5">
         <v>1</v>
       </c>
     </row>
@@ -22677,8 +22717,10 @@
     <hyperlink ref="H519" r:id="rId987" xr:uid="{F8A797C3-2C08-44C6-9C4B-3E67DCA94155}"/>
     <hyperlink ref="E520" r:id="rId988" xr:uid="{43570C22-BEB1-4F31-91A8-E6109AE9A2BC}"/>
     <hyperlink ref="H520" r:id="rId989" xr:uid="{A5D96057-849F-42B3-9419-CA8A37EF8E5B}"/>
+    <hyperlink ref="E521" r:id="rId990" xr:uid="{2D6923BE-9BCE-4080-BBFB-41EFB0BD49C4}"/>
+    <hyperlink ref="H521" r:id="rId991" xr:uid="{89D34C3B-1968-4960-8797-032A37CB9A99}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId990"/>
+  <pageSetup orientation="portrait" r:id="rId992"/>
 </worksheet>
 </file>
--- a/docs/CodeSignal/record.xlsx
+++ b/docs/CodeSignal/record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\everyday-use\Blog\docs\CodeSignal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{174BA40E-8B66-413E-909E-F81677E5F6A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{060E07D9-C32C-430E-934E-F1225BEFEBAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" tabRatio="511" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2092" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2096" uniqueCount="120">
   <si>
     <t>番号</t>
   </si>
@@ -947,7 +947,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:L521"/>
+  <dimension ref="A1:L522"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="7.7265625" style="10" bestFit="1" customWidth="1"/>
@@ -13446,7 +13446,7 @@
     </row>
     <row r="315" spans="1:12" ht="24" customHeight="1">
       <c r="A315" s="5">
-        <f t="shared" ref="A315:A521" si="8">ROW()-1</f>
+        <f t="shared" ref="A315:A522" si="8">ROW()-1</f>
         <v>314</v>
       </c>
       <c r="B315" s="6">
@@ -19330,7 +19330,7 @@
         <v>461</v>
       </c>
       <c r="B462" s="6">
-        <f t="shared" ref="B462:B521" si="10">B461+1</f>
+        <f t="shared" ref="B462:B522" si="10">B461+1</f>
         <v>46223</v>
       </c>
       <c r="C462" s="5">
@@ -21694,7 +21694,7 @@
         <v>46282</v>
       </c>
       <c r="C521" s="5">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="D521" s="15" t="s">
         <v>112</v>
@@ -21721,6 +21721,46 @@
         <v>1</v>
       </c>
       <c r="L521" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="522" spans="1:12" ht="24" customHeight="1">
+      <c r="A522" s="5">
+        <f t="shared" si="8"/>
+        <v>521</v>
+      </c>
+      <c r="B522" s="6">
+        <f t="shared" si="10"/>
+        <v>46283</v>
+      </c>
+      <c r="C522" s="5">
+        <v>818</v>
+      </c>
+      <c r="D522" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="E522" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="F522" s="5">
+        <v>4</v>
+      </c>
+      <c r="G522" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="H522" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="I522" s="9">
+        <v>0.37</v>
+      </c>
+      <c r="J522" s="5">
+        <v>2</v>
+      </c>
+      <c r="K522" s="5">
+        <v>1</v>
+      </c>
+      <c r="L522" s="5">
         <v>1</v>
       </c>
     </row>
@@ -22719,8 +22759,10 @@
     <hyperlink ref="H520" r:id="rId989" xr:uid="{A5D96057-849F-42B3-9419-CA8A37EF8E5B}"/>
     <hyperlink ref="E521" r:id="rId990" xr:uid="{2D6923BE-9BCE-4080-BBFB-41EFB0BD49C4}"/>
     <hyperlink ref="H521" r:id="rId991" xr:uid="{89D34C3B-1968-4960-8797-032A37CB9A99}"/>
+    <hyperlink ref="E522" r:id="rId992" xr:uid="{ED958DFE-0DF7-4816-861A-5F1F4E4B039D}"/>
+    <hyperlink ref="H522" r:id="rId993" xr:uid="{B631BE52-FFFE-4591-AC7A-CB0E308DBFC1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId992"/>
+  <pageSetup orientation="portrait" r:id="rId994"/>
 </worksheet>
 </file>
--- a/docs/CodeSignal/record.xlsx
+++ b/docs/CodeSignal/record.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\everyday-use\Blog\docs\CodeSignal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{060E07D9-C32C-430E-934E-F1225BEFEBAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E29D1E50-2AC6-4756-BA4D-F87B260690E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" tabRatio="511" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19020" yWindow="0" windowWidth="19380" windowHeight="20970" tabRatio="511" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CodeSignalの記録" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2096" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2100" uniqueCount="120">
   <si>
     <t>番号</t>
   </si>
@@ -947,7 +947,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:L522"/>
+  <dimension ref="A1:L523"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="7.7265625" style="10" bestFit="1" customWidth="1"/>
@@ -13446,7 +13446,7 @@
     </row>
     <row r="315" spans="1:12" ht="24" customHeight="1">
       <c r="A315" s="5">
-        <f t="shared" ref="A315:A522" si="8">ROW()-1</f>
+        <f t="shared" ref="A315:A523" si="8">ROW()-1</f>
         <v>314</v>
       </c>
       <c r="B315" s="6">
@@ -19330,7 +19330,7 @@
         <v>461</v>
       </c>
       <c r="B462" s="6">
-        <f t="shared" ref="B462:B522" si="10">B461+1</f>
+        <f t="shared" ref="B462:B523" si="10">B461+1</f>
         <v>46223</v>
       </c>
       <c r="C462" s="5">
@@ -21762,6 +21762,46 @@
       </c>
       <c r="L522" s="5">
         <v>1</v>
+      </c>
+    </row>
+    <row r="523" spans="1:12" ht="24" customHeight="1">
+      <c r="A523" s="5">
+        <f t="shared" si="8"/>
+        <v>522</v>
+      </c>
+      <c r="B523" s="6">
+        <f t="shared" si="10"/>
+        <v>46284</v>
+      </c>
+      <c r="C523" s="5">
+        <v>818</v>
+      </c>
+      <c r="D523" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="E523" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="F523" s="5">
+        <v>4</v>
+      </c>
+      <c r="G523" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="H523" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="I523" s="9">
+        <v>0.37</v>
+      </c>
+      <c r="J523" s="5">
+        <v>2</v>
+      </c>
+      <c r="K523" s="5">
+        <v>0</v>
+      </c>
+      <c r="L523" s="5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -22761,8 +22801,10 @@
     <hyperlink ref="H521" r:id="rId991" xr:uid="{89D34C3B-1968-4960-8797-032A37CB9A99}"/>
     <hyperlink ref="E522" r:id="rId992" xr:uid="{ED958DFE-0DF7-4816-861A-5F1F4E4B039D}"/>
     <hyperlink ref="H522" r:id="rId993" xr:uid="{B631BE52-FFFE-4591-AC7A-CB0E308DBFC1}"/>
+    <hyperlink ref="E523" r:id="rId994" xr:uid="{37502FB7-6D1C-42D3-AACF-7BFF7E9F4072}"/>
+    <hyperlink ref="H523" r:id="rId995" xr:uid="{9807EE87-FEBF-4ABF-96B2-354A5DB7D2B3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId994"/>
+  <pageSetup orientation="portrait" r:id="rId996"/>
 </worksheet>
 </file>
--- a/docs/CodeSignal/record.xlsx
+++ b/docs/CodeSignal/record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\everyday-use\Blog\docs\CodeSignal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E29D1E50-2AC6-4756-BA4D-F87B260690E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE8F3878-FFEC-4790-830F-E87F3455810E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19020" yWindow="0" windowWidth="19380" windowHeight="20970" tabRatio="511" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2100" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2104" uniqueCount="120">
   <si>
     <t>番号</t>
   </si>
@@ -947,7 +947,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:L523"/>
+  <dimension ref="A1:L524"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="7.7265625" style="10" bestFit="1" customWidth="1"/>
@@ -13446,7 +13446,7 @@
     </row>
     <row r="315" spans="1:12" ht="24" customHeight="1">
       <c r="A315" s="5">
-        <f t="shared" ref="A315:A523" si="8">ROW()-1</f>
+        <f t="shared" ref="A315:A524" si="8">ROW()-1</f>
         <v>314</v>
       </c>
       <c r="B315" s="6">
@@ -19330,7 +19330,7 @@
         <v>461</v>
       </c>
       <c r="B462" s="6">
-        <f t="shared" ref="B462:B523" si="10">B461+1</f>
+        <f t="shared" ref="B462:B524" si="10">B461+1</f>
         <v>46223</v>
       </c>
       <c r="C462" s="5">
@@ -21802,6 +21802,46 @@
       </c>
       <c r="L523" s="5">
         <v>0</v>
+      </c>
+    </row>
+    <row r="524" spans="1:12" ht="24" customHeight="1">
+      <c r="A524" s="5">
+        <f t="shared" si="8"/>
+        <v>523</v>
+      </c>
+      <c r="B524" s="6">
+        <f t="shared" si="10"/>
+        <v>46285</v>
+      </c>
+      <c r="C524" s="5">
+        <v>819</v>
+      </c>
+      <c r="D524" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="E524" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="F524" s="5">
+        <v>4</v>
+      </c>
+      <c r="G524" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="H524" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="I524" s="9">
+        <v>0.4</v>
+      </c>
+      <c r="J524" s="5">
+        <v>2</v>
+      </c>
+      <c r="K524" s="5">
+        <v>1</v>
+      </c>
+      <c r="L524" s="5">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -22803,8 +22843,10 @@
     <hyperlink ref="H522" r:id="rId993" xr:uid="{B631BE52-FFFE-4591-AC7A-CB0E308DBFC1}"/>
     <hyperlink ref="E523" r:id="rId994" xr:uid="{37502FB7-6D1C-42D3-AACF-7BFF7E9F4072}"/>
     <hyperlink ref="H523" r:id="rId995" xr:uid="{9807EE87-FEBF-4ABF-96B2-354A5DB7D2B3}"/>
+    <hyperlink ref="E524" r:id="rId996" xr:uid="{5D95D178-B4F4-452E-BD0A-D24ABA065563}"/>
+    <hyperlink ref="H524" r:id="rId997" xr:uid="{4228B4A8-ECA2-48DF-B822-8B733BADE2C5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId996"/>
+  <pageSetup orientation="portrait" r:id="rId998"/>
 </worksheet>
 </file>
--- a/docs/CodeSignal/record.xlsx
+++ b/docs/CodeSignal/record.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\everyday-use\Blog\docs\CodeSignal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE8F3878-FFEC-4790-830F-E87F3455810E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60802F4D-C108-49FD-86B3-6D5631B62413}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19020" yWindow="0" windowWidth="19380" windowHeight="20970" tabRatio="511" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" tabRatio="511" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CodeSignalの記録" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2104" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2108" uniqueCount="120">
   <si>
     <t>番号</t>
   </si>
@@ -947,7 +947,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:L524"/>
+  <dimension ref="A1:L525"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="7.7265625" style="10" bestFit="1" customWidth="1"/>
@@ -13446,7 +13446,7 @@
     </row>
     <row r="315" spans="1:12" ht="24" customHeight="1">
       <c r="A315" s="5">
-        <f t="shared" ref="A315:A524" si="8">ROW()-1</f>
+        <f t="shared" ref="A315:A525" si="8">ROW()-1</f>
         <v>314</v>
       </c>
       <c r="B315" s="6">
@@ -19330,7 +19330,7 @@
         <v>461</v>
       </c>
       <c r="B462" s="6">
-        <f t="shared" ref="B462:B524" si="10">B461+1</f>
+        <f t="shared" ref="B462:B525" si="10">B461+1</f>
         <v>46223</v>
       </c>
       <c r="C462" s="5">
@@ -21842,6 +21842,46 @@
       </c>
       <c r="L524" s="5">
         <v>1</v>
+      </c>
+    </row>
+    <row r="525" spans="1:12" ht="24" customHeight="1">
+      <c r="A525" s="5">
+        <f t="shared" si="8"/>
+        <v>524</v>
+      </c>
+      <c r="B525" s="6">
+        <f t="shared" si="10"/>
+        <v>46286</v>
+      </c>
+      <c r="C525" s="5">
+        <v>820</v>
+      </c>
+      <c r="D525" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="E525" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="F525" s="5">
+        <v>4</v>
+      </c>
+      <c r="G525" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="H525" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="I525" s="9">
+        <v>0.44</v>
+      </c>
+      <c r="J525" s="5">
+        <v>2</v>
+      </c>
+      <c r="K525" s="5">
+        <v>0</v>
+      </c>
+      <c r="L525" s="5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -22845,8 +22885,10 @@
     <hyperlink ref="H523" r:id="rId995" xr:uid="{9807EE87-FEBF-4ABF-96B2-354A5DB7D2B3}"/>
     <hyperlink ref="E524" r:id="rId996" xr:uid="{5D95D178-B4F4-452E-BD0A-D24ABA065563}"/>
     <hyperlink ref="H524" r:id="rId997" xr:uid="{4228B4A8-ECA2-48DF-B822-8B733BADE2C5}"/>
+    <hyperlink ref="E525" r:id="rId998" xr:uid="{AE95DCF5-35EE-4992-99FB-7533C5AAC7D0}"/>
+    <hyperlink ref="H525" r:id="rId999" xr:uid="{B69DC19F-0398-4466-91F6-4225441C5AFE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId998"/>
+  <pageSetup orientation="portrait" r:id="rId1000"/>
 </worksheet>
 </file>
--- a/docs/CodeSignal/record.xlsx
+++ b/docs/CodeSignal/record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\everyday-use\Blog\docs\CodeSignal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60802F4D-C108-49FD-86B3-6D5631B62413}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{166E89C7-A235-4C2A-A869-CC59CF244113}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" tabRatio="511" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2108" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2112" uniqueCount="120">
   <si>
     <t>番号</t>
   </si>
@@ -947,7 +947,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:L525"/>
+  <dimension ref="A1:L526"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="7.7265625" style="10" bestFit="1" customWidth="1"/>
@@ -13446,7 +13446,7 @@
     </row>
     <row r="315" spans="1:12" ht="24" customHeight="1">
       <c r="A315" s="5">
-        <f t="shared" ref="A315:A525" si="8">ROW()-1</f>
+        <f t="shared" ref="A315:A526" si="8">ROW()-1</f>
         <v>314</v>
       </c>
       <c r="B315" s="6">
@@ -19330,7 +19330,7 @@
         <v>461</v>
       </c>
       <c r="B462" s="6">
-        <f t="shared" ref="B462:B525" si="10">B461+1</f>
+        <f t="shared" ref="B462:B526" si="10">B461+1</f>
         <v>46223</v>
       </c>
       <c r="C462" s="5">
@@ -21882,6 +21882,46 @@
       </c>
       <c r="L525" s="5">
         <v>0</v>
+      </c>
+    </row>
+    <row r="526" spans="1:12" ht="24" customHeight="1">
+      <c r="A526" s="5">
+        <f t="shared" si="8"/>
+        <v>525</v>
+      </c>
+      <c r="B526" s="6">
+        <f t="shared" si="10"/>
+        <v>46287</v>
+      </c>
+      <c r="C526" s="5">
+        <v>821</v>
+      </c>
+      <c r="D526" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="E526" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="F526" s="5">
+        <v>4</v>
+      </c>
+      <c r="G526" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="H526" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="I526" s="9">
+        <v>0.48</v>
+      </c>
+      <c r="J526" s="5">
+        <v>2</v>
+      </c>
+      <c r="K526" s="5">
+        <v>1</v>
+      </c>
+      <c r="L526" s="5">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -22887,8 +22927,10 @@
     <hyperlink ref="H524" r:id="rId997" xr:uid="{4228B4A8-ECA2-48DF-B822-8B733BADE2C5}"/>
     <hyperlink ref="E525" r:id="rId998" xr:uid="{AE95DCF5-35EE-4992-99FB-7533C5AAC7D0}"/>
     <hyperlink ref="H525" r:id="rId999" xr:uid="{B69DC19F-0398-4466-91F6-4225441C5AFE}"/>
+    <hyperlink ref="E526" r:id="rId1000" xr:uid="{ECC8ACE5-7CC9-4FE6-8FA1-D4C18819A928}"/>
+    <hyperlink ref="H526" r:id="rId1001" xr:uid="{79C627AE-215A-4153-A76A-B042A81B9F5E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1000"/>
+  <pageSetup orientation="portrait" r:id="rId1002"/>
 </worksheet>
 </file>
--- a/docs/CodeSignal/record.xlsx
+++ b/docs/CodeSignal/record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\everyday-use\Blog\docs\CodeSignal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{166E89C7-A235-4C2A-A869-CC59CF244113}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B35B98E-5EAB-4A9D-9B89-CFD5FEB38540}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" tabRatio="511" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2112" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2116" uniqueCount="120">
   <si>
     <t>番号</t>
   </si>
@@ -947,7 +947,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:L526"/>
+  <dimension ref="A1:L527"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="7.7265625" style="10" bestFit="1" customWidth="1"/>
@@ -13446,7 +13446,7 @@
     </row>
     <row r="315" spans="1:12" ht="24" customHeight="1">
       <c r="A315" s="5">
-        <f t="shared" ref="A315:A526" si="8">ROW()-1</f>
+        <f t="shared" ref="A315:A527" si="8">ROW()-1</f>
         <v>314</v>
       </c>
       <c r="B315" s="6">
@@ -19330,7 +19330,7 @@
         <v>461</v>
       </c>
       <c r="B462" s="6">
-        <f t="shared" ref="B462:B526" si="10">B461+1</f>
+        <f t="shared" ref="B462:B527" si="10">B461+1</f>
         <v>46223</v>
       </c>
       <c r="C462" s="5">
@@ -21921,6 +21921,46 @@
         <v>1</v>
       </c>
       <c r="L526" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="527" spans="1:12" ht="24" customHeight="1">
+      <c r="A527" s="5">
+        <f t="shared" si="8"/>
+        <v>526</v>
+      </c>
+      <c r="B527" s="6">
+        <f t="shared" si="10"/>
+        <v>46288</v>
+      </c>
+      <c r="C527" s="5">
+        <v>822</v>
+      </c>
+      <c r="D527" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="E527" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="F527" s="5">
+        <v>4</v>
+      </c>
+      <c r="G527" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="H527" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="I527" s="9">
+        <v>0.52</v>
+      </c>
+      <c r="J527" s="5">
+        <v>2</v>
+      </c>
+      <c r="K527" s="5">
+        <v>1</v>
+      </c>
+      <c r="L527" s="5">
         <v>1</v>
       </c>
     </row>
@@ -22929,8 +22969,10 @@
     <hyperlink ref="H525" r:id="rId999" xr:uid="{B69DC19F-0398-4466-91F6-4225441C5AFE}"/>
     <hyperlink ref="E526" r:id="rId1000" xr:uid="{ECC8ACE5-7CC9-4FE6-8FA1-D4C18819A928}"/>
     <hyperlink ref="H526" r:id="rId1001" xr:uid="{79C627AE-215A-4153-A76A-B042A81B9F5E}"/>
+    <hyperlink ref="E527" r:id="rId1002" xr:uid="{FF8F5299-90B1-4C98-9E0B-07B1B209B481}"/>
+    <hyperlink ref="H527" r:id="rId1003" xr:uid="{E9BC679E-77DC-418D-B51D-542629E02495}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1002"/>
+  <pageSetup orientation="portrait" r:id="rId1004"/>
 </worksheet>
 </file>
--- a/docs/CodeSignal/record.xlsx
+++ b/docs/CodeSignal/record.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\everyday-use\Blog\docs\CodeSignal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B35B98E-5EAB-4A9D-9B89-CFD5FEB38540}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26954AB6-5694-4FC2-AEF0-ED82C1DE6941}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" tabRatio="511" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2116" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2120" uniqueCount="120">
   <si>
     <t>番号</t>
   </si>
@@ -947,7 +947,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:L527"/>
+  <dimension ref="A1:L528"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="7.7265625" style="10" bestFit="1" customWidth="1"/>
@@ -13446,7 +13446,7 @@
     </row>
     <row r="315" spans="1:12" ht="24" customHeight="1">
       <c r="A315" s="5">
-        <f t="shared" ref="A315:A527" si="8">ROW()-1</f>
+        <f t="shared" ref="A315:A528" si="8">ROW()-1</f>
         <v>314</v>
       </c>
       <c r="B315" s="6">
@@ -19330,7 +19330,7 @@
         <v>461</v>
       </c>
       <c r="B462" s="6">
-        <f t="shared" ref="B462:B527" si="10">B461+1</f>
+        <f t="shared" ref="B462:B528" si="10">B461+1</f>
         <v>46223</v>
       </c>
       <c r="C462" s="5">
@@ -21961,6 +21961,46 @@
         <v>1</v>
       </c>
       <c r="L527" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="528" spans="1:12" ht="24" customHeight="1">
+      <c r="A528" s="5">
+        <f t="shared" si="8"/>
+        <v>527</v>
+      </c>
+      <c r="B528" s="6">
+        <f t="shared" si="10"/>
+        <v>46289</v>
+      </c>
+      <c r="C528" s="5">
+        <v>823</v>
+      </c>
+      <c r="D528" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="E528" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="F528" s="5">
+        <v>4</v>
+      </c>
+      <c r="G528" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="H528" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="I528" s="9">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="J528" s="5">
+        <v>2</v>
+      </c>
+      <c r="K528" s="5">
+        <v>1</v>
+      </c>
+      <c r="L528" s="5">
         <v>1</v>
       </c>
     </row>
@@ -22971,8 +23011,10 @@
     <hyperlink ref="H526" r:id="rId1001" xr:uid="{79C627AE-215A-4153-A76A-B042A81B9F5E}"/>
     <hyperlink ref="E527" r:id="rId1002" xr:uid="{FF8F5299-90B1-4C98-9E0B-07B1B209B481}"/>
     <hyperlink ref="H527" r:id="rId1003" xr:uid="{E9BC679E-77DC-418D-B51D-542629E02495}"/>
+    <hyperlink ref="E528" r:id="rId1004" xr:uid="{CD2DCADF-3E3C-43B7-B06A-A941BA500E02}"/>
+    <hyperlink ref="H528" r:id="rId1005" xr:uid="{6651825B-749B-46E6-9ED6-71038EB1D320}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1004"/>
+  <pageSetup orientation="portrait" r:id="rId1006"/>
 </worksheet>
 </file>
--- a/docs/CodeSignal/record.xlsx
+++ b/docs/CodeSignal/record.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\everyday-use\Blog\docs\CodeSignal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26954AB6-5694-4FC2-AEF0-ED82C1DE6941}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC034825-1339-4754-8910-E6D8C1E1FD52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" tabRatio="511" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19020" yWindow="0" windowWidth="19380" windowHeight="20970" tabRatio="511" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CodeSignalの記録" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2120" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2124" uniqueCount="120">
   <si>
     <t>番号</t>
   </si>
@@ -947,7 +947,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:L528"/>
+  <dimension ref="A1:L529"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="7.7265625" style="10" bestFit="1" customWidth="1"/>
@@ -13446,7 +13446,7 @@
     </row>
     <row r="315" spans="1:12" ht="24" customHeight="1">
       <c r="A315" s="5">
-        <f t="shared" ref="A315:A528" si="8">ROW()-1</f>
+        <f t="shared" ref="A315:A529" si="8">ROW()-1</f>
         <v>314</v>
       </c>
       <c r="B315" s="6">
@@ -19330,7 +19330,7 @@
         <v>461</v>
       </c>
       <c r="B462" s="6">
-        <f t="shared" ref="B462:B528" si="10">B461+1</f>
+        <f t="shared" ref="B462:B529" si="10">B461+1</f>
         <v>46223</v>
       </c>
       <c r="C462" s="5">
@@ -22002,6 +22002,46 @@
       </c>
       <c r="L528" s="5">
         <v>1</v>
+      </c>
+    </row>
+    <row r="529" spans="1:12" ht="24" customHeight="1">
+      <c r="A529" s="5">
+        <f t="shared" si="8"/>
+        <v>528</v>
+      </c>
+      <c r="B529" s="6">
+        <f t="shared" si="10"/>
+        <v>46290</v>
+      </c>
+      <c r="C529" s="5">
+        <v>823</v>
+      </c>
+      <c r="D529" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="E529" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="F529" s="5">
+        <v>4</v>
+      </c>
+      <c r="G529" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="H529" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="I529" s="9">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="J529" s="5">
+        <v>2</v>
+      </c>
+      <c r="K529" s="5">
+        <v>0</v>
+      </c>
+      <c r="L529" s="5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -23013,8 +23053,10 @@
     <hyperlink ref="H527" r:id="rId1003" xr:uid="{E9BC679E-77DC-418D-B51D-542629E02495}"/>
     <hyperlink ref="E528" r:id="rId1004" xr:uid="{CD2DCADF-3E3C-43B7-B06A-A941BA500E02}"/>
     <hyperlink ref="H528" r:id="rId1005" xr:uid="{6651825B-749B-46E6-9ED6-71038EB1D320}"/>
+    <hyperlink ref="E529" r:id="rId1006" xr:uid="{A5CB9DBA-CC10-41BB-9014-5432006D329D}"/>
+    <hyperlink ref="H529" r:id="rId1007" xr:uid="{B8625B5B-A959-49A3-BB3F-1BE21C0C59A3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1006"/>
+  <pageSetup orientation="portrait" r:id="rId1008"/>
 </worksheet>
 </file>
--- a/docs/CodeSignal/record.xlsx
+++ b/docs/CodeSignal/record.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\everyday-use\Blog\docs\CodeSignal\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\everyday-use\Blog\docs\CodeSignal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC034825-1339-4754-8910-E6D8C1E1FD52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FC6E3CE-B94B-48A9-8060-41DBAC69D3BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19020" yWindow="0" windowWidth="19380" windowHeight="20970" tabRatio="511" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" tabRatio="511" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CodeSignalの記録" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2124" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2128" uniqueCount="120">
   <si>
     <t>番号</t>
   </si>
@@ -947,7 +947,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:L529"/>
+  <dimension ref="A1:L530"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="7.7265625" style="10" bestFit="1" customWidth="1"/>
@@ -13446,7 +13446,7 @@
     </row>
     <row r="315" spans="1:12" ht="24" customHeight="1">
       <c r="A315" s="5">
-        <f t="shared" ref="A315:A529" si="8">ROW()-1</f>
+        <f t="shared" ref="A315:A530" si="8">ROW()-1</f>
         <v>314</v>
       </c>
       <c r="B315" s="6">
@@ -19330,7 +19330,7 @@
         <v>461</v>
       </c>
       <c r="B462" s="6">
-        <f t="shared" ref="B462:B529" si="10">B461+1</f>
+        <f t="shared" ref="B462:B530" si="10">B461+1</f>
         <v>46223</v>
       </c>
       <c r="C462" s="5">
@@ -22041,6 +22041,46 @@
         <v>0</v>
       </c>
       <c r="L529" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="530" spans="1:12" ht="24" customHeight="1">
+      <c r="A530" s="5">
+        <f t="shared" si="8"/>
+        <v>529</v>
+      </c>
+      <c r="B530" s="6">
+        <f t="shared" si="10"/>
+        <v>46291</v>
+      </c>
+      <c r="C530" s="5">
+        <v>823</v>
+      </c>
+      <c r="D530" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="E530" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="F530" s="5">
+        <v>4</v>
+      </c>
+      <c r="G530" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="H530" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="I530" s="9">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="J530" s="5">
+        <v>2</v>
+      </c>
+      <c r="K530" s="5">
+        <v>0</v>
+      </c>
+      <c r="L530" s="5">
         <v>0</v>
       </c>
     </row>
@@ -23055,8 +23095,10 @@
     <hyperlink ref="H528" r:id="rId1005" xr:uid="{6651825B-749B-46E6-9ED6-71038EB1D320}"/>
     <hyperlink ref="E529" r:id="rId1006" xr:uid="{A5CB9DBA-CC10-41BB-9014-5432006D329D}"/>
     <hyperlink ref="H529" r:id="rId1007" xr:uid="{B8625B5B-A959-49A3-BB3F-1BE21C0C59A3}"/>
+    <hyperlink ref="E530" r:id="rId1008" xr:uid="{6A056991-3CC0-4287-AE3A-BF8CC5BAD234}"/>
+    <hyperlink ref="H530" r:id="rId1009" xr:uid="{EC28695C-E2C3-44A8-822F-F98E72DA82DF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1008"/>
+  <pageSetup orientation="portrait" r:id="rId1010"/>
 </worksheet>
 </file>
--- a/docs/CodeSignal/record.xlsx
+++ b/docs/CodeSignal/record.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\everyday-use\Blog\docs\CodeSignal\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\everyday-use\Blog\docs\CodeSignal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FC6E3CE-B94B-48A9-8060-41DBAC69D3BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4B5D158-648F-434F-AB6A-8226EAC7C226}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" tabRatio="511" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2128" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2132" uniqueCount="120">
   <si>
     <t>番号</t>
   </si>
@@ -947,7 +947,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:L530"/>
+  <dimension ref="A1:L531"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="7.7265625" style="10" bestFit="1" customWidth="1"/>
@@ -13446,7 +13446,7 @@
     </row>
     <row r="315" spans="1:12" ht="24" customHeight="1">
       <c r="A315" s="5">
-        <f t="shared" ref="A315:A530" si="8">ROW()-1</f>
+        <f t="shared" ref="A315:A531" si="8">ROW()-1</f>
         <v>314</v>
       </c>
       <c r="B315" s="6">
@@ -19330,7 +19330,7 @@
         <v>461</v>
       </c>
       <c r="B462" s="6">
-        <f t="shared" ref="B462:B530" si="10">B461+1</f>
+        <f t="shared" ref="B462:B531" si="10">B461+1</f>
         <v>46223</v>
       </c>
       <c r="C462" s="5">
@@ -22082,6 +22082,46 @@
       </c>
       <c r="L530" s="5">
         <v>0</v>
+      </c>
+    </row>
+    <row r="531" spans="1:12" ht="24" customHeight="1">
+      <c r="A531" s="5">
+        <f t="shared" si="8"/>
+        <v>530</v>
+      </c>
+      <c r="B531" s="6">
+        <f t="shared" si="10"/>
+        <v>46292</v>
+      </c>
+      <c r="C531" s="5">
+        <v>824</v>
+      </c>
+      <c r="D531" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="E531" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="F531" s="5">
+        <v>4</v>
+      </c>
+      <c r="G531" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="H531" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="I531" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="J531" s="5">
+        <v>2</v>
+      </c>
+      <c r="K531" s="5">
+        <v>1</v>
+      </c>
+      <c r="L531" s="5">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -23097,8 +23137,10 @@
     <hyperlink ref="H529" r:id="rId1007" xr:uid="{B8625B5B-A959-49A3-BB3F-1BE21C0C59A3}"/>
     <hyperlink ref="E530" r:id="rId1008" xr:uid="{6A056991-3CC0-4287-AE3A-BF8CC5BAD234}"/>
     <hyperlink ref="H530" r:id="rId1009" xr:uid="{EC28695C-E2C3-44A8-822F-F98E72DA82DF}"/>
+    <hyperlink ref="E531" r:id="rId1010" xr:uid="{242213BD-5488-4C6C-A17C-7FF7BD94C3E1}"/>
+    <hyperlink ref="H531" r:id="rId1011" xr:uid="{9D18FC47-BB7E-4DD0-A99C-731F15E5BCF1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1010"/>
+  <pageSetup orientation="portrait" r:id="rId1012"/>
 </worksheet>
 </file>
--- a/docs/CodeSignal/record.xlsx
+++ b/docs/CodeSignal/record.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\everyday-use\Blog\docs\CodeSignal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4B5D158-648F-434F-AB6A-8226EAC7C226}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12DD7A3F-66BA-4D0D-B076-F8DB6ACEE9C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" tabRatio="511" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19020" yWindow="0" windowWidth="19380" windowHeight="20970" tabRatio="511" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CodeSignalの記録" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2132" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2136" uniqueCount="120">
   <si>
     <t>番号</t>
   </si>
@@ -947,7 +947,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:L531"/>
+  <dimension ref="A1:L532"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="7.7265625" style="10" bestFit="1" customWidth="1"/>
@@ -13446,7 +13446,7 @@
     </row>
     <row r="315" spans="1:12" ht="24" customHeight="1">
       <c r="A315" s="5">
-        <f t="shared" ref="A315:A531" si="8">ROW()-1</f>
+        <f t="shared" ref="A315:A532" si="8">ROW()-1</f>
         <v>314</v>
       </c>
       <c r="B315" s="6">
@@ -19330,7 +19330,7 @@
         <v>461</v>
       </c>
       <c r="B462" s="6">
-        <f t="shared" ref="B462:B531" si="10">B461+1</f>
+        <f t="shared" ref="B462:B532" si="10">B461+1</f>
         <v>46223</v>
       </c>
       <c r="C462" s="5">
@@ -22122,6 +22122,46 @@
       </c>
       <c r="L531" s="5">
         <v>1</v>
+      </c>
+    </row>
+    <row r="532" spans="1:12" ht="24" customHeight="1">
+      <c r="A532" s="5">
+        <f t="shared" si="8"/>
+        <v>531</v>
+      </c>
+      <c r="B532" s="6">
+        <f t="shared" si="10"/>
+        <v>46293</v>
+      </c>
+      <c r="C532" s="5">
+        <v>825</v>
+      </c>
+      <c r="D532" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="E532" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="F532" s="5">
+        <v>4</v>
+      </c>
+      <c r="G532" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="H532" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="I532" s="9">
+        <v>0.64</v>
+      </c>
+      <c r="J532" s="5">
+        <v>2</v>
+      </c>
+      <c r="K532" s="5">
+        <v>0</v>
+      </c>
+      <c r="L532" s="5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -23139,8 +23179,10 @@
     <hyperlink ref="H530" r:id="rId1009" xr:uid="{EC28695C-E2C3-44A8-822F-F98E72DA82DF}"/>
     <hyperlink ref="E531" r:id="rId1010" xr:uid="{242213BD-5488-4C6C-A17C-7FF7BD94C3E1}"/>
     <hyperlink ref="H531" r:id="rId1011" xr:uid="{9D18FC47-BB7E-4DD0-A99C-731F15E5BCF1}"/>
+    <hyperlink ref="E532" r:id="rId1012" xr:uid="{3AF9686D-9768-488A-A380-F52014438274}"/>
+    <hyperlink ref="H532" r:id="rId1013" xr:uid="{E8118F00-B512-43FC-A3B0-0B87B6F55F57}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1012"/>
+  <pageSetup orientation="portrait" r:id="rId1014"/>
 </worksheet>
 </file>
--- a/docs/CodeSignal/record.xlsx
+++ b/docs/CodeSignal/record.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\everyday-use\Blog\docs\CodeSignal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12DD7A3F-66BA-4D0D-B076-F8DB6ACEE9C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFB2BC84-424F-41DE-B94B-B6CF565BE543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19020" yWindow="0" windowWidth="19380" windowHeight="20970" tabRatio="511" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19110" yWindow="0" windowWidth="19290" windowHeight="20880" tabRatio="511" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CodeSignalの記録" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2136" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2140" uniqueCount="120">
   <si>
     <t>番号</t>
   </si>
@@ -947,7 +947,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:L532"/>
+  <dimension ref="A1:L533"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="7.7265625" style="10" bestFit="1" customWidth="1"/>
@@ -13446,7 +13446,7 @@
     </row>
     <row r="315" spans="1:12" ht="24" customHeight="1">
       <c r="A315" s="5">
-        <f t="shared" ref="A315:A532" si="8">ROW()-1</f>
+        <f t="shared" ref="A315:A533" si="8">ROW()-1</f>
         <v>314</v>
       </c>
       <c r="B315" s="6">
@@ -19330,7 +19330,7 @@
         <v>461</v>
       </c>
       <c r="B462" s="6">
-        <f t="shared" ref="B462:B532" si="10">B461+1</f>
+        <f t="shared" ref="B462:B533" si="10">B461+1</f>
         <v>46223</v>
       </c>
       <c r="C462" s="5">
@@ -22161,6 +22161,46 @@
         <v>0</v>
       </c>
       <c r="L532" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="533" spans="1:12" ht="24" customHeight="1">
+      <c r="A533" s="5">
+        <f t="shared" si="8"/>
+        <v>532</v>
+      </c>
+      <c r="B533" s="6">
+        <f t="shared" si="10"/>
+        <v>46294</v>
+      </c>
+      <c r="C533" s="5">
+        <v>825</v>
+      </c>
+      <c r="D533" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="E533" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="F533" s="5">
+        <v>4</v>
+      </c>
+      <c r="G533" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="H533" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="I533" s="9">
+        <v>0.64</v>
+      </c>
+      <c r="J533" s="5">
+        <v>2</v>
+      </c>
+      <c r="K533" s="5">
+        <v>0</v>
+      </c>
+      <c r="L533" s="5">
         <v>0</v>
       </c>
     </row>
@@ -23181,8 +23221,10 @@
     <hyperlink ref="H531" r:id="rId1011" xr:uid="{9D18FC47-BB7E-4DD0-A99C-731F15E5BCF1}"/>
     <hyperlink ref="E532" r:id="rId1012" xr:uid="{3AF9686D-9768-488A-A380-F52014438274}"/>
     <hyperlink ref="H532" r:id="rId1013" xr:uid="{E8118F00-B512-43FC-A3B0-0B87B6F55F57}"/>
+    <hyperlink ref="E533" r:id="rId1014" xr:uid="{4F9B5304-55E1-4ACF-BBFD-28A373A0932D}"/>
+    <hyperlink ref="H533" r:id="rId1015" xr:uid="{4016884B-B24F-4A94-9E20-06A937F5BC32}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1014"/>
+  <pageSetup orientation="portrait" r:id="rId1016"/>
 </worksheet>
 </file>
--- a/docs/CodeSignal/record.xlsx
+++ b/docs/CodeSignal/record.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\everyday-use\Blog\docs\CodeSignal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFB2BC84-424F-41DE-B94B-B6CF565BE543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0D30D9D-40A5-4983-B57B-E7A53613FC50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19110" yWindow="0" windowWidth="19290" windowHeight="20880" tabRatio="511" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" tabRatio="511" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CodeSignalの記録" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2140" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2144" uniqueCount="120">
   <si>
     <t>番号</t>
   </si>
@@ -947,7 +947,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:L533"/>
+  <dimension ref="A1:L534"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="7.7265625" style="10" bestFit="1" customWidth="1"/>
@@ -13446,7 +13446,7 @@
     </row>
     <row r="315" spans="1:12" ht="24" customHeight="1">
       <c r="A315" s="5">
-        <f t="shared" ref="A315:A533" si="8">ROW()-1</f>
+        <f t="shared" ref="A315:A534" si="8">ROW()-1</f>
         <v>314</v>
       </c>
       <c r="B315" s="6">
@@ -19330,7 +19330,7 @@
         <v>461</v>
       </c>
       <c r="B462" s="6">
-        <f t="shared" ref="B462:B533" si="10">B461+1</f>
+        <f t="shared" ref="B462:B534" si="10">B461+1</f>
         <v>46223</v>
       </c>
       <c r="C462" s="5">
@@ -22202,6 +22202,46 @@
       </c>
       <c r="L533" s="5">
         <v>0</v>
+      </c>
+    </row>
+    <row r="534" spans="1:12" ht="24" customHeight="1">
+      <c r="A534" s="5">
+        <f t="shared" si="8"/>
+        <v>533</v>
+      </c>
+      <c r="B534" s="6">
+        <f t="shared" si="10"/>
+        <v>46295</v>
+      </c>
+      <c r="C534" s="5">
+        <v>826</v>
+      </c>
+      <c r="D534" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="E534" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="F534" s="5">
+        <v>4</v>
+      </c>
+      <c r="G534" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="H534" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="I534" s="9">
+        <v>0.68</v>
+      </c>
+      <c r="J534" s="5">
+        <v>2</v>
+      </c>
+      <c r="K534" s="5">
+        <v>1</v>
+      </c>
+      <c r="L534" s="5">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -23223,8 +23263,10 @@
     <hyperlink ref="H532" r:id="rId1013" xr:uid="{E8118F00-B512-43FC-A3B0-0B87B6F55F57}"/>
     <hyperlink ref="E533" r:id="rId1014" xr:uid="{4F9B5304-55E1-4ACF-BBFD-28A373A0932D}"/>
     <hyperlink ref="H533" r:id="rId1015" xr:uid="{4016884B-B24F-4A94-9E20-06A937F5BC32}"/>
+    <hyperlink ref="E534" r:id="rId1016" xr:uid="{DE7FC08A-AC30-42A5-8451-1CE5BCB9A35B}"/>
+    <hyperlink ref="H534" r:id="rId1017" xr:uid="{D315198F-484B-49FA-AD3A-123233B72BE2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1016"/>
+  <pageSetup orientation="portrait" r:id="rId1018"/>
 </worksheet>
 </file>
--- a/docs/CodeSignal/record.xlsx
+++ b/docs/CodeSignal/record.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\everyday-use\Blog\docs\CodeSignal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0D30D9D-40A5-4983-B57B-E7A53613FC50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E621695-68C6-452D-A165-ADDAF0ACBA80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" tabRatio="511" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19020" yWindow="0" windowWidth="19380" windowHeight="20970" tabRatio="511" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CodeSignalの記録" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2144" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2148" uniqueCount="120">
   <si>
     <t>番号</t>
   </si>
@@ -947,7 +947,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:L534"/>
+  <dimension ref="A1:L535"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="7.7265625" style="10" bestFit="1" customWidth="1"/>
@@ -13446,7 +13446,7 @@
     </row>
     <row r="315" spans="1:12" ht="24" customHeight="1">
       <c r="A315" s="5">
-        <f t="shared" ref="A315:A534" si="8">ROW()-1</f>
+        <f t="shared" ref="A315:A535" si="8">ROW()-1</f>
         <v>314</v>
       </c>
       <c r="B315" s="6">
@@ -19330,7 +19330,7 @@
         <v>461</v>
       </c>
       <c r="B462" s="6">
-        <f t="shared" ref="B462:B534" si="10">B461+1</f>
+        <f t="shared" ref="B462:B535" si="10">B461+1</f>
         <v>46223</v>
       </c>
       <c r="C462" s="5">
@@ -22242,6 +22242,46 @@
       </c>
       <c r="L534" s="5">
         <v>1</v>
+      </c>
+    </row>
+    <row r="535" spans="1:12" ht="24" customHeight="1">
+      <c r="A535" s="5">
+        <f t="shared" si="8"/>
+        <v>534</v>
+      </c>
+      <c r="B535" s="6">
+        <f t="shared" si="10"/>
+        <v>46296</v>
+      </c>
+      <c r="C535" s="5">
+        <v>826</v>
+      </c>
+      <c r="D535" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="E535" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="F535" s="5">
+        <v>4</v>
+      </c>
+      <c r="G535" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="H535" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="I535" s="9">
+        <v>0.68</v>
+      </c>
+      <c r="J535" s="5">
+        <v>2</v>
+      </c>
+      <c r="K535" s="5">
+        <v>0</v>
+      </c>
+      <c r="L535" s="5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -23265,8 +23305,10 @@
     <hyperlink ref="H533" r:id="rId1015" xr:uid="{4016884B-B24F-4A94-9E20-06A937F5BC32}"/>
     <hyperlink ref="E534" r:id="rId1016" xr:uid="{DE7FC08A-AC30-42A5-8451-1CE5BCB9A35B}"/>
     <hyperlink ref="H534" r:id="rId1017" xr:uid="{D315198F-484B-49FA-AD3A-123233B72BE2}"/>
+    <hyperlink ref="E535" r:id="rId1018" xr:uid="{F36B56DE-2B11-466F-8B2A-B81B386D215E}"/>
+    <hyperlink ref="H535" r:id="rId1019" xr:uid="{316C7EA7-CD75-4B08-9AE9-153CED715034}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1018"/>
+  <pageSetup orientation="portrait" r:id="rId1020"/>
 </worksheet>
 </file>
--- a/docs/CodeSignal/record.xlsx
+++ b/docs/CodeSignal/record.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\everyday-use\Blog\docs\CodeSignal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E621695-68C6-452D-A165-ADDAF0ACBA80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3CB99D8-FCCC-4A4F-8CE3-7EFB05D3B555}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19020" yWindow="0" windowWidth="19380" windowHeight="20970" tabRatio="511" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" tabRatio="511" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CodeSignalの記録" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2148" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2152" uniqueCount="120">
   <si>
     <t>番号</t>
   </si>
@@ -947,7 +947,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:L535"/>
+  <dimension ref="A1:L536"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="7.7265625" style="10" bestFit="1" customWidth="1"/>
@@ -13446,7 +13446,7 @@
     </row>
     <row r="315" spans="1:12" ht="24" customHeight="1">
       <c r="A315" s="5">
-        <f t="shared" ref="A315:A535" si="8">ROW()-1</f>
+        <f t="shared" ref="A315:A536" si="8">ROW()-1</f>
         <v>314</v>
       </c>
       <c r="B315" s="6">
@@ -19330,7 +19330,7 @@
         <v>461</v>
       </c>
       <c r="B462" s="6">
-        <f t="shared" ref="B462:B535" si="10">B461+1</f>
+        <f t="shared" ref="B462:B536" si="10">B461+1</f>
         <v>46223</v>
       </c>
       <c r="C462" s="5">
@@ -22282,6 +22282,46 @@
       </c>
       <c r="L535" s="5">
         <v>0</v>
+      </c>
+    </row>
+    <row r="536" spans="1:12" ht="24" customHeight="1">
+      <c r="A536" s="5">
+        <f t="shared" si="8"/>
+        <v>535</v>
+      </c>
+      <c r="B536" s="6">
+        <f t="shared" si="10"/>
+        <v>46297</v>
+      </c>
+      <c r="C536" s="5">
+        <v>827</v>
+      </c>
+      <c r="D536" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="E536" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="F536" s="5">
+        <v>4</v>
+      </c>
+      <c r="G536" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="H536" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="I536" s="9">
+        <v>0.72</v>
+      </c>
+      <c r="J536" s="5">
+        <v>2</v>
+      </c>
+      <c r="K536" s="5">
+        <v>1</v>
+      </c>
+      <c r="L536" s="5">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -23307,8 +23347,10 @@
     <hyperlink ref="H534" r:id="rId1017" xr:uid="{D315198F-484B-49FA-AD3A-123233B72BE2}"/>
     <hyperlink ref="E535" r:id="rId1018" xr:uid="{F36B56DE-2B11-466F-8B2A-B81B386D215E}"/>
     <hyperlink ref="H535" r:id="rId1019" xr:uid="{316C7EA7-CD75-4B08-9AE9-153CED715034}"/>
+    <hyperlink ref="E536" r:id="rId1020" xr:uid="{F4B16279-893F-4DBC-B817-15CABCA68C28}"/>
+    <hyperlink ref="H536" r:id="rId1021" xr:uid="{5B10F56B-4D38-4F2B-9E01-6ED19C170930}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1020"/>
+  <pageSetup orientation="portrait" r:id="rId1022"/>
 </worksheet>
 </file>
--- a/docs/CodeSignal/record.xlsx
+++ b/docs/CodeSignal/record.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\everyday-use\Blog\docs\CodeSignal\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\everyday-use\Blog\docs\CodeSignal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3CB99D8-FCCC-4A4F-8CE3-7EFB05D3B555}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DA74975-6D2B-4E44-AA87-C4B2F071D7A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" tabRatio="511" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2560" yWindow="1980" windowWidth="28800" windowHeight="15260" tabRatio="511" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CodeSignalの記録" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2152" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2156" uniqueCount="120">
   <si>
     <t>番号</t>
   </si>
@@ -947,7 +947,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:L536"/>
+  <dimension ref="A1:L537"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="7.7265625" style="10" bestFit="1" customWidth="1"/>
@@ -13446,7 +13446,7 @@
     </row>
     <row r="315" spans="1:12" ht="24" customHeight="1">
       <c r="A315" s="5">
-        <f t="shared" ref="A315:A536" si="8">ROW()-1</f>
+        <f t="shared" ref="A315:A537" si="8">ROW()-1</f>
         <v>314</v>
       </c>
       <c r="B315" s="6">
@@ -19330,7 +19330,7 @@
         <v>461</v>
       </c>
       <c r="B462" s="6">
-        <f t="shared" ref="B462:B536" si="10">B461+1</f>
+        <f t="shared" ref="B462:B537" si="10">B461+1</f>
         <v>46223</v>
       </c>
       <c r="C462" s="5">
@@ -22322,6 +22322,46 @@
       </c>
       <c r="L536" s="5">
         <v>1</v>
+      </c>
+    </row>
+    <row r="537" spans="1:12" ht="24" customHeight="1">
+      <c r="A537" s="5">
+        <f t="shared" si="8"/>
+        <v>536</v>
+      </c>
+      <c r="B537" s="6">
+        <f t="shared" si="10"/>
+        <v>46298</v>
+      </c>
+      <c r="C537" s="5">
+        <v>827</v>
+      </c>
+      <c r="D537" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="E537" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="F537" s="5">
+        <v>4</v>
+      </c>
+      <c r="G537" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="H537" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="I537" s="9">
+        <v>0.72</v>
+      </c>
+      <c r="J537" s="5">
+        <v>2</v>
+      </c>
+      <c r="K537" s="5">
+        <v>0</v>
+      </c>
+      <c r="L537" s="5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -23349,8 +23389,10 @@
     <hyperlink ref="H535" r:id="rId1019" xr:uid="{316C7EA7-CD75-4B08-9AE9-153CED715034}"/>
     <hyperlink ref="E536" r:id="rId1020" xr:uid="{F4B16279-893F-4DBC-B817-15CABCA68C28}"/>
     <hyperlink ref="H536" r:id="rId1021" xr:uid="{5B10F56B-4D38-4F2B-9E01-6ED19C170930}"/>
+    <hyperlink ref="E537" r:id="rId1022" xr:uid="{C30AE1D0-2D85-47F3-BFD4-2E21BB04174E}"/>
+    <hyperlink ref="H537" r:id="rId1023" xr:uid="{D32D1BC9-2C42-4FAF-8D59-E730FA9574B9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1022"/>
+  <pageSetup orientation="portrait" r:id="rId1024"/>
 </worksheet>
 </file>
--- a/docs/CodeSignal/record.xlsx
+++ b/docs/CodeSignal/record.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\everyday-use\Blog\docs\CodeSignal\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\everyday-use\Blog\docs\CodeSignal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DA74975-6D2B-4E44-AA87-C4B2F071D7A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48A8BF4E-9C48-41D4-B94C-99DDD3A23970}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2560" yWindow="1980" windowWidth="28800" windowHeight="15260" tabRatio="511" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="511" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CodeSignalの記録" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2156" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2160" uniqueCount="120">
   <si>
     <t>番号</t>
   </si>
@@ -947,7 +947,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:L537"/>
+  <dimension ref="A1:L538"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="7.7265625" style="10" bestFit="1" customWidth="1"/>
@@ -13446,7 +13446,7 @@
     </row>
     <row r="315" spans="1:12" ht="24" customHeight="1">
       <c r="A315" s="5">
-        <f t="shared" ref="A315:A537" si="8">ROW()-1</f>
+        <f t="shared" ref="A315:A538" si="8">ROW()-1</f>
         <v>314</v>
       </c>
       <c r="B315" s="6">
@@ -19330,7 +19330,7 @@
         <v>461</v>
       </c>
       <c r="B462" s="6">
-        <f t="shared" ref="B462:B537" si="10">B461+1</f>
+        <f t="shared" ref="B462:B538" si="10">B461+1</f>
         <v>46223</v>
       </c>
       <c r="C462" s="5">
@@ -22361,6 +22361,46 @@
         <v>0</v>
       </c>
       <c r="L537" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="538" spans="1:12" ht="24" customHeight="1">
+      <c r="A538" s="5">
+        <f t="shared" si="8"/>
+        <v>537</v>
+      </c>
+      <c r="B538" s="6">
+        <f t="shared" si="10"/>
+        <v>46299</v>
+      </c>
+      <c r="C538" s="5">
+        <v>827</v>
+      </c>
+      <c r="D538" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="E538" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="F538" s="5">
+        <v>4</v>
+      </c>
+      <c r="G538" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="H538" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="I538" s="9">
+        <v>0.72</v>
+      </c>
+      <c r="J538" s="5">
+        <v>2</v>
+      </c>
+      <c r="K538" s="5">
+        <v>0</v>
+      </c>
+      <c r="L538" s="5">
         <v>0</v>
       </c>
     </row>
@@ -23391,8 +23431,10 @@
     <hyperlink ref="H536" r:id="rId1021" xr:uid="{5B10F56B-4D38-4F2B-9E01-6ED19C170930}"/>
     <hyperlink ref="E537" r:id="rId1022" xr:uid="{C30AE1D0-2D85-47F3-BFD4-2E21BB04174E}"/>
     <hyperlink ref="H537" r:id="rId1023" xr:uid="{D32D1BC9-2C42-4FAF-8D59-E730FA9574B9}"/>
+    <hyperlink ref="E538" r:id="rId1024" xr:uid="{43EF2869-A90F-4D67-A8A8-52671A7167DD}"/>
+    <hyperlink ref="H538" r:id="rId1025" xr:uid="{942CD62D-16CD-49C4-A5F3-37E61BA1A364}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1024"/>
+  <pageSetup orientation="portrait" r:id="rId1026"/>
 </worksheet>
 </file>
--- a/docs/CodeSignal/record.xlsx
+++ b/docs/CodeSignal/record.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\everyday-use\Blog\docs\CodeSignal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48A8BF4E-9C48-41D4-B94C-99DDD3A23970}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{103C4FA3-6806-48C7-B0D0-3262A2E9F082}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="511" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" tabRatio="511" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CodeSignalの記録" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2160" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2164" uniqueCount="120">
   <si>
     <t>番号</t>
   </si>
@@ -947,7 +947,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:L538"/>
+  <dimension ref="A1:L539"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="7.7265625" style="10" bestFit="1" customWidth="1"/>
@@ -13446,7 +13446,7 @@
     </row>
     <row r="315" spans="1:12" ht="24" customHeight="1">
       <c r="A315" s="5">
-        <f t="shared" ref="A315:A538" si="8">ROW()-1</f>
+        <f t="shared" ref="A315:A539" si="8">ROW()-1</f>
         <v>314</v>
       </c>
       <c r="B315" s="6">
@@ -19330,7 +19330,7 @@
         <v>461</v>
       </c>
       <c r="B462" s="6">
-        <f t="shared" ref="B462:B538" si="10">B461+1</f>
+        <f t="shared" ref="B462:B539" si="10">B461+1</f>
         <v>46223</v>
       </c>
       <c r="C462" s="5">
@@ -22402,6 +22402,46 @@
       </c>
       <c r="L538" s="5">
         <v>0</v>
+      </c>
+    </row>
+    <row r="539" spans="1:12" ht="24" customHeight="1">
+      <c r="A539" s="5">
+        <f t="shared" si="8"/>
+        <v>538</v>
+      </c>
+      <c r="B539" s="6">
+        <f t="shared" si="10"/>
+        <v>46300</v>
+      </c>
+      <c r="C539" s="5">
+        <v>828</v>
+      </c>
+      <c r="D539" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="E539" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="F539" s="5">
+        <v>4</v>
+      </c>
+      <c r="G539" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="H539" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="I539" s="9">
+        <v>0.76</v>
+      </c>
+      <c r="J539" s="5">
+        <v>2</v>
+      </c>
+      <c r="K539" s="5">
+        <v>1</v>
+      </c>
+      <c r="L539" s="5">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -23433,8 +23473,10 @@
     <hyperlink ref="H537" r:id="rId1023" xr:uid="{D32D1BC9-2C42-4FAF-8D59-E730FA9574B9}"/>
     <hyperlink ref="E538" r:id="rId1024" xr:uid="{43EF2869-A90F-4D67-A8A8-52671A7167DD}"/>
     <hyperlink ref="H538" r:id="rId1025" xr:uid="{942CD62D-16CD-49C4-A5F3-37E61BA1A364}"/>
+    <hyperlink ref="E539" r:id="rId1026" xr:uid="{13EC0528-7A59-47BB-9EEF-8C488535D05A}"/>
+    <hyperlink ref="H539" r:id="rId1027" xr:uid="{8727ECFC-0FF3-4FA9-B358-CEC37DE98DCB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1026"/>
+  <pageSetup orientation="portrait" r:id="rId1028"/>
 </worksheet>
 </file>
--- a/docs/CodeSignal/record.xlsx
+++ b/docs/CodeSignal/record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\everyday-use\Blog\docs\CodeSignal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{103C4FA3-6806-48C7-B0D0-3262A2E9F082}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95930485-8661-4874-A886-6307A1950F6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" tabRatio="511" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2164" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2168" uniqueCount="120">
   <si>
     <t>番号</t>
   </si>
@@ -947,7 +947,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:L539"/>
+  <dimension ref="A1:L540"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="7.7265625" style="10" bestFit="1" customWidth="1"/>
@@ -13446,7 +13446,7 @@
     </row>
     <row r="315" spans="1:12" ht="24" customHeight="1">
       <c r="A315" s="5">
-        <f t="shared" ref="A315:A539" si="8">ROW()-1</f>
+        <f t="shared" ref="A315:A540" si="8">ROW()-1</f>
         <v>314</v>
       </c>
       <c r="B315" s="6">
@@ -19330,7 +19330,7 @@
         <v>461</v>
       </c>
       <c r="B462" s="6">
-        <f t="shared" ref="B462:B539" si="10">B461+1</f>
+        <f t="shared" ref="B462:B540" si="10">B461+1</f>
         <v>46223</v>
       </c>
       <c r="C462" s="5">
@@ -22441,6 +22441,46 @@
         <v>1</v>
       </c>
       <c r="L539" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="540" spans="1:12" ht="24" customHeight="1">
+      <c r="A540" s="5">
+        <f t="shared" si="8"/>
+        <v>539</v>
+      </c>
+      <c r="B540" s="6">
+        <f t="shared" si="10"/>
+        <v>46301</v>
+      </c>
+      <c r="C540" s="5">
+        <v>829</v>
+      </c>
+      <c r="D540" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="E540" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="F540" s="5">
+        <v>4</v>
+      </c>
+      <c r="G540" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="H540" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="I540" s="9">
+        <v>0.8</v>
+      </c>
+      <c r="J540" s="5">
+        <v>2</v>
+      </c>
+      <c r="K540" s="5">
+        <v>1</v>
+      </c>
+      <c r="L540" s="5">
         <v>1</v>
       </c>
     </row>
@@ -23475,8 +23515,10 @@
     <hyperlink ref="H538" r:id="rId1025" xr:uid="{942CD62D-16CD-49C4-A5F3-37E61BA1A364}"/>
     <hyperlink ref="E539" r:id="rId1026" xr:uid="{13EC0528-7A59-47BB-9EEF-8C488535D05A}"/>
     <hyperlink ref="H539" r:id="rId1027" xr:uid="{8727ECFC-0FF3-4FA9-B358-CEC37DE98DCB}"/>
+    <hyperlink ref="E540" r:id="rId1028" xr:uid="{60B84191-7EB4-4910-9236-A5C9699F077D}"/>
+    <hyperlink ref="H540" r:id="rId1029" xr:uid="{C40BA1A6-DE05-4D2A-A942-56634FD52895}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1028"/>
+  <pageSetup orientation="portrait" r:id="rId1030"/>
 </worksheet>
 </file>
--- a/docs/CodeSignal/record.xlsx
+++ b/docs/CodeSignal/record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\everyday-use\Blog\docs\CodeSignal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95930485-8661-4874-A886-6307A1950F6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E6DDF01-23EA-4D84-BF68-2EEC9C5F8F25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" tabRatio="511" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2168" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2172" uniqueCount="120">
   <si>
     <t>番号</t>
   </si>
@@ -947,7 +947,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:L540"/>
+  <dimension ref="A1:L541"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="7.7265625" style="10" bestFit="1" customWidth="1"/>
@@ -13446,7 +13446,7 @@
     </row>
     <row r="315" spans="1:12" ht="24" customHeight="1">
       <c r="A315" s="5">
-        <f t="shared" ref="A315:A540" si="8">ROW()-1</f>
+        <f t="shared" ref="A315:A541" si="8">ROW()-1</f>
         <v>314</v>
       </c>
       <c r="B315" s="6">
@@ -19330,7 +19330,7 @@
         <v>461</v>
       </c>
       <c r="B462" s="6">
-        <f t="shared" ref="B462:B540" si="10">B461+1</f>
+        <f t="shared" ref="B462:B541" si="10">B461+1</f>
         <v>46223</v>
       </c>
       <c r="C462" s="5">
@@ -22482,6 +22482,46 @@
       </c>
       <c r="L540" s="5">
         <v>1</v>
+      </c>
+    </row>
+    <row r="541" spans="1:12" ht="24" customHeight="1">
+      <c r="A541" s="5">
+        <f t="shared" si="8"/>
+        <v>540</v>
+      </c>
+      <c r="B541" s="6">
+        <f t="shared" si="10"/>
+        <v>46302</v>
+      </c>
+      <c r="C541" s="5">
+        <v>829</v>
+      </c>
+      <c r="D541" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="E541" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="F541" s="5">
+        <v>4</v>
+      </c>
+      <c r="G541" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="H541" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="I541" s="9">
+        <v>0.8</v>
+      </c>
+      <c r="J541" s="5">
+        <v>2</v>
+      </c>
+      <c r="K541" s="5">
+        <v>0</v>
+      </c>
+      <c r="L541" s="5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -23517,8 +23557,10 @@
     <hyperlink ref="H539" r:id="rId1027" xr:uid="{8727ECFC-0FF3-4FA9-B358-CEC37DE98DCB}"/>
     <hyperlink ref="E540" r:id="rId1028" xr:uid="{60B84191-7EB4-4910-9236-A5C9699F077D}"/>
     <hyperlink ref="H540" r:id="rId1029" xr:uid="{C40BA1A6-DE05-4D2A-A942-56634FD52895}"/>
+    <hyperlink ref="E541" r:id="rId1030" xr:uid="{6315FC71-D408-435A-ABE2-044AC6D096C5}"/>
+    <hyperlink ref="H541" r:id="rId1031" xr:uid="{117A9EBA-46C3-4282-9E9D-13FA50A4F4DE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1030"/>
+  <pageSetup orientation="portrait" r:id="rId1032"/>
 </worksheet>
 </file>
--- a/docs/CodeSignal/record.xlsx
+++ b/docs/CodeSignal/record.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\everyday-use\Blog\docs\CodeSignal\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\everyday-use\Blog\docs\CodeSignal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E6DDF01-23EA-4D84-BF68-2EEC9C5F8F25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{078F1004-DA18-4563-8D86-82A77E9CE3FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" tabRatio="511" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2172" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2176" uniqueCount="120">
   <si>
     <t>番号</t>
   </si>
@@ -947,7 +947,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:L541"/>
+  <dimension ref="A1:L542"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="7.7265625" style="10" bestFit="1" customWidth="1"/>
@@ -13446,7 +13446,7 @@
     </row>
     <row r="315" spans="1:12" ht="24" customHeight="1">
       <c r="A315" s="5">
-        <f t="shared" ref="A315:A541" si="8">ROW()-1</f>
+        <f t="shared" ref="A315:A542" si="8">ROW()-1</f>
         <v>314</v>
       </c>
       <c r="B315" s="6">
@@ -19330,7 +19330,7 @@
         <v>461</v>
       </c>
       <c r="B462" s="6">
-        <f t="shared" ref="B462:B541" si="10">B461+1</f>
+        <f t="shared" ref="B462:B542" si="10">B461+1</f>
         <v>46223</v>
       </c>
       <c r="C462" s="5">
@@ -22521,6 +22521,46 @@
         <v>0</v>
       </c>
       <c r="L541" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="542" spans="1:12" ht="24" customHeight="1">
+      <c r="A542" s="5">
+        <f t="shared" si="8"/>
+        <v>541</v>
+      </c>
+      <c r="B542" s="6">
+        <f t="shared" si="10"/>
+        <v>46303</v>
+      </c>
+      <c r="C542" s="5">
+        <v>830</v>
+      </c>
+      <c r="D542" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="E542" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="F542" s="5">
+        <v>4</v>
+      </c>
+      <c r="G542" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="H542" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="I542" s="9">
+        <v>0.84</v>
+      </c>
+      <c r="J542" s="5">
+        <v>2</v>
+      </c>
+      <c r="K542" s="5">
+        <v>0</v>
+      </c>
+      <c r="L542" s="5">
         <v>0</v>
       </c>
     </row>
@@ -23559,8 +23599,10 @@
     <hyperlink ref="H540" r:id="rId1029" xr:uid="{C40BA1A6-DE05-4D2A-A942-56634FD52895}"/>
     <hyperlink ref="E541" r:id="rId1030" xr:uid="{6315FC71-D408-435A-ABE2-044AC6D096C5}"/>
     <hyperlink ref="H541" r:id="rId1031" xr:uid="{117A9EBA-46C3-4282-9E9D-13FA50A4F4DE}"/>
+    <hyperlink ref="E542" r:id="rId1032" xr:uid="{61B65524-DB86-43E5-91C5-300617B5A029}"/>
+    <hyperlink ref="H542" r:id="rId1033" xr:uid="{2B143377-EF3C-412B-8989-A17943C50AE2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1032"/>
+  <pageSetup orientation="portrait" r:id="rId1034"/>
 </worksheet>
 </file>
--- a/docs/CodeSignal/record.xlsx
+++ b/docs/CodeSignal/record.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\everyday-use\Blog\docs\CodeSignal\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\everyday-use\Blog\docs\CodeSignal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{078F1004-DA18-4563-8D86-82A77E9CE3FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45E6798A-AEE5-49A8-B939-FCF6F1D929BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" tabRatio="511" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2176" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2180" uniqueCount="120">
   <si>
     <t>番号</t>
   </si>
@@ -947,7 +947,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:L542"/>
+  <dimension ref="A1:L543"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="7.7265625" style="10" bestFit="1" customWidth="1"/>
@@ -13446,7 +13446,7 @@
     </row>
     <row r="315" spans="1:12" ht="24" customHeight="1">
       <c r="A315" s="5">
-        <f t="shared" ref="A315:A542" si="8">ROW()-1</f>
+        <f t="shared" ref="A315:A543" si="8">ROW()-1</f>
         <v>314</v>
       </c>
       <c r="B315" s="6">
@@ -19330,7 +19330,7 @@
         <v>461</v>
       </c>
       <c r="B462" s="6">
-        <f t="shared" ref="B462:B542" si="10">B461+1</f>
+        <f t="shared" ref="B462:B543" si="10">B461+1</f>
         <v>46223</v>
       </c>
       <c r="C462" s="5">
@@ -22561,6 +22561,46 @@
         <v>0</v>
       </c>
       <c r="L542" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="543" spans="1:12" ht="24" customHeight="1">
+      <c r="A543" s="5">
+        <f t="shared" si="8"/>
+        <v>542</v>
+      </c>
+      <c r="B543" s="6">
+        <f t="shared" si="10"/>
+        <v>46304</v>
+      </c>
+      <c r="C543" s="5">
+        <v>830</v>
+      </c>
+      <c r="D543" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="E543" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="F543" s="5">
+        <v>4</v>
+      </c>
+      <c r="G543" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="H543" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="I543" s="9">
+        <v>0.84</v>
+      </c>
+      <c r="J543" s="5">
+        <v>2</v>
+      </c>
+      <c r="K543" s="5">
+        <v>0</v>
+      </c>
+      <c r="L543" s="5">
         <v>0</v>
       </c>
     </row>
@@ -23601,8 +23641,10 @@
     <hyperlink ref="H541" r:id="rId1031" xr:uid="{117A9EBA-46C3-4282-9E9D-13FA50A4F4DE}"/>
     <hyperlink ref="E542" r:id="rId1032" xr:uid="{61B65524-DB86-43E5-91C5-300617B5A029}"/>
     <hyperlink ref="H542" r:id="rId1033" xr:uid="{2B143377-EF3C-412B-8989-A17943C50AE2}"/>
+    <hyperlink ref="E543" r:id="rId1034" xr:uid="{C723F67F-9F39-4D9A-9818-2284ED03D2BC}"/>
+    <hyperlink ref="H543" r:id="rId1035" xr:uid="{93E79F96-8D16-42E2-A1BB-53B4CAD09728}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1034"/>
+  <pageSetup orientation="portrait" r:id="rId1036"/>
 </worksheet>
 </file>
--- a/docs/CodeSignal/record.xlsx
+++ b/docs/CodeSignal/record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\everyday-use\Blog\docs\CodeSignal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45E6798A-AEE5-49A8-B939-FCF6F1D929BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA1B4CB0-63D4-400F-908B-51A858E9C044}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" tabRatio="511" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2180" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2184" uniqueCount="120">
   <si>
     <t>番号</t>
   </si>
@@ -947,7 +947,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:L543"/>
+  <dimension ref="A1:L544"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="7.7265625" style="10" bestFit="1" customWidth="1"/>
@@ -13446,7 +13446,7 @@
     </row>
     <row r="315" spans="1:12" ht="24" customHeight="1">
       <c r="A315" s="5">
-        <f t="shared" ref="A315:A543" si="8">ROW()-1</f>
+        <f t="shared" ref="A315:A544" si="8">ROW()-1</f>
         <v>314</v>
       </c>
       <c r="B315" s="6">
@@ -19330,7 +19330,7 @@
         <v>461</v>
       </c>
       <c r="B462" s="6">
-        <f t="shared" ref="B462:B543" si="10">B461+1</f>
+        <f t="shared" ref="B462:B544" si="10">B461+1</f>
         <v>46223</v>
       </c>
       <c r="C462" s="5">
@@ -22602,6 +22602,46 @@
       </c>
       <c r="L543" s="5">
         <v>0</v>
+      </c>
+    </row>
+    <row r="544" spans="1:12" ht="24" customHeight="1">
+      <c r="A544" s="5">
+        <f t="shared" si="8"/>
+        <v>543</v>
+      </c>
+      <c r="B544" s="6">
+        <f t="shared" si="10"/>
+        <v>46305</v>
+      </c>
+      <c r="C544" s="5">
+        <v>831</v>
+      </c>
+      <c r="D544" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="E544" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="F544" s="5">
+        <v>4</v>
+      </c>
+      <c r="G544" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="H544" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="I544" s="9">
+        <v>0.88</v>
+      </c>
+      <c r="J544" s="5">
+        <v>2</v>
+      </c>
+      <c r="K544" s="5">
+        <v>1</v>
+      </c>
+      <c r="L544" s="5">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -23643,8 +23683,10 @@
     <hyperlink ref="H542" r:id="rId1033" xr:uid="{2B143377-EF3C-412B-8989-A17943C50AE2}"/>
     <hyperlink ref="E543" r:id="rId1034" xr:uid="{C723F67F-9F39-4D9A-9818-2284ED03D2BC}"/>
     <hyperlink ref="H543" r:id="rId1035" xr:uid="{93E79F96-8D16-42E2-A1BB-53B4CAD09728}"/>
+    <hyperlink ref="E544" r:id="rId1036" xr:uid="{39404785-2BFF-4008-ABE0-8EFB2F653AB8}"/>
+    <hyperlink ref="H544" r:id="rId1037" xr:uid="{333B5A76-BB86-44B3-B511-FD54B60827DB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1036"/>
+  <pageSetup orientation="portrait" r:id="rId1038"/>
 </worksheet>
 </file>
--- a/docs/CodeSignal/record.xlsx
+++ b/docs/CodeSignal/record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\everyday-use\Blog\docs\CodeSignal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA1B4CB0-63D4-400F-908B-51A858E9C044}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B98E61B8-6429-4210-9213-D77571C0F3C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" tabRatio="511" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2184" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2188" uniqueCount="120">
   <si>
     <t>番号</t>
   </si>
@@ -947,7 +947,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:L544"/>
+  <dimension ref="A1:L545"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="7.7265625" style="10" bestFit="1" customWidth="1"/>
@@ -13446,7 +13446,7 @@
     </row>
     <row r="315" spans="1:12" ht="24" customHeight="1">
       <c r="A315" s="5">
-        <f t="shared" ref="A315:A544" si="8">ROW()-1</f>
+        <f t="shared" ref="A315:A545" si="8">ROW()-1</f>
         <v>314</v>
       </c>
       <c r="B315" s="6">
@@ -19330,7 +19330,7 @@
         <v>461</v>
       </c>
       <c r="B462" s="6">
-        <f t="shared" ref="B462:B544" si="10">B461+1</f>
+        <f t="shared" ref="B462:B545" si="10">B461+1</f>
         <v>46223</v>
       </c>
       <c r="C462" s="5">
@@ -22641,6 +22641,46 @@
         <v>1</v>
       </c>
       <c r="L544" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="545" spans="1:12" ht="24" customHeight="1">
+      <c r="A545" s="5">
+        <f t="shared" si="8"/>
+        <v>544</v>
+      </c>
+      <c r="B545" s="6">
+        <f t="shared" si="10"/>
+        <v>46306</v>
+      </c>
+      <c r="C545" s="5">
+        <v>832</v>
+      </c>
+      <c r="D545" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="E545" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="F545" s="5">
+        <v>4</v>
+      </c>
+      <c r="G545" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="H545" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="I545" s="9">
+        <v>0.92</v>
+      </c>
+      <c r="J545" s="5">
+        <v>2</v>
+      </c>
+      <c r="K545" s="5">
+        <v>1</v>
+      </c>
+      <c r="L545" s="5">
         <v>1</v>
       </c>
     </row>
@@ -23685,8 +23725,10 @@
     <hyperlink ref="H543" r:id="rId1035" xr:uid="{93E79F96-8D16-42E2-A1BB-53B4CAD09728}"/>
     <hyperlink ref="E544" r:id="rId1036" xr:uid="{39404785-2BFF-4008-ABE0-8EFB2F653AB8}"/>
     <hyperlink ref="H544" r:id="rId1037" xr:uid="{333B5A76-BB86-44B3-B511-FD54B60827DB}"/>
+    <hyperlink ref="E545" r:id="rId1038" xr:uid="{A77EFED4-4539-40D6-A595-BE38DBE8B3DE}"/>
+    <hyperlink ref="H545" r:id="rId1039" xr:uid="{66D5F5FA-0904-41C3-96F1-3185DF1AE153}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1038"/>
+  <pageSetup orientation="portrait" r:id="rId1040"/>
 </worksheet>
 </file>
--- a/docs/CodeSignal/record.xlsx
+++ b/docs/CodeSignal/record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\everyday-use\Blog\docs\CodeSignal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B98E61B8-6429-4210-9213-D77571C0F3C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{658E5CB5-8486-4199-880D-D0F1F0105A7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" tabRatio="511" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2188" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2192" uniqueCount="120">
   <si>
     <t>番号</t>
   </si>
@@ -947,7 +947,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:L545"/>
+  <dimension ref="A1:L546"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="7.7265625" style="10" bestFit="1" customWidth="1"/>
@@ -13446,7 +13446,7 @@
     </row>
     <row r="315" spans="1:12" ht="24" customHeight="1">
       <c r="A315" s="5">
-        <f t="shared" ref="A315:A545" si="8">ROW()-1</f>
+        <f t="shared" ref="A315:A546" si="8">ROW()-1</f>
         <v>314</v>
       </c>
       <c r="B315" s="6">
@@ -19330,7 +19330,7 @@
         <v>461</v>
       </c>
       <c r="B462" s="6">
-        <f t="shared" ref="B462:B545" si="10">B461+1</f>
+        <f t="shared" ref="B462:B546" si="10">B461+1</f>
         <v>46223</v>
       </c>
       <c r="C462" s="5">
@@ -22681,6 +22681,46 @@
         <v>1</v>
       </c>
       <c r="L545" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="546" spans="1:12" ht="24" customHeight="1">
+      <c r="A546" s="5">
+        <f t="shared" si="8"/>
+        <v>545</v>
+      </c>
+      <c r="B546" s="6">
+        <f t="shared" si="10"/>
+        <v>46307</v>
+      </c>
+      <c r="C546" s="5">
+        <v>833</v>
+      </c>
+      <c r="D546" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="E546" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="F546" s="5">
+        <v>4</v>
+      </c>
+      <c r="G546" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="H546" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="I546" s="9">
+        <v>0.96</v>
+      </c>
+      <c r="J546" s="5">
+        <v>2</v>
+      </c>
+      <c r="K546" s="5">
+        <v>1</v>
+      </c>
+      <c r="L546" s="5">
         <v>1</v>
       </c>
     </row>
@@ -23727,8 +23767,10 @@
     <hyperlink ref="H544" r:id="rId1037" xr:uid="{333B5A76-BB86-44B3-B511-FD54B60827DB}"/>
     <hyperlink ref="E545" r:id="rId1038" xr:uid="{A77EFED4-4539-40D6-A595-BE38DBE8B3DE}"/>
     <hyperlink ref="H545" r:id="rId1039" xr:uid="{66D5F5FA-0904-41C3-96F1-3185DF1AE153}"/>
+    <hyperlink ref="E546" r:id="rId1040" xr:uid="{3DF07115-41AD-47DE-8A0A-6817CAD07E4F}"/>
+    <hyperlink ref="H546" r:id="rId1041" xr:uid="{A3AC0014-61BD-4649-90B6-9AC2C895FEA4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1040"/>
+  <pageSetup orientation="portrait" r:id="rId1042"/>
 </worksheet>
 </file>
--- a/docs/CodeSignal/record.xlsx
+++ b/docs/CodeSignal/record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\everyday-use\Blog\docs\CodeSignal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{658E5CB5-8486-4199-880D-D0F1F0105A7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D30805EA-2D64-4B5A-91B0-09574A7A9D88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" tabRatio="511" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2192" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2196" uniqueCount="120">
   <si>
     <t>番号</t>
   </si>
@@ -947,7 +947,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:L546"/>
+  <dimension ref="A1:L547"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="7.7265625" style="10" bestFit="1" customWidth="1"/>
@@ -13446,7 +13446,7 @@
     </row>
     <row r="315" spans="1:12" ht="24" customHeight="1">
       <c r="A315" s="5">
-        <f t="shared" ref="A315:A546" si="8">ROW()-1</f>
+        <f t="shared" ref="A315:A547" si="8">ROW()-1</f>
         <v>314</v>
       </c>
       <c r="B315" s="6">
@@ -19330,7 +19330,7 @@
         <v>461</v>
       </c>
       <c r="B462" s="6">
-        <f t="shared" ref="B462:B546" si="10">B461+1</f>
+        <f t="shared" ref="B462:B547" si="10">B461+1</f>
         <v>46223</v>
       </c>
       <c r="C462" s="5">
@@ -22721,6 +22721,46 @@
         <v>1</v>
       </c>
       <c r="L546" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="547" spans="1:12" ht="24" customHeight="1">
+      <c r="A547" s="5">
+        <f t="shared" si="8"/>
+        <v>546</v>
+      </c>
+      <c r="B547" s="6">
+        <f t="shared" si="10"/>
+        <v>46308</v>
+      </c>
+      <c r="C547" s="5">
+        <v>833</v>
+      </c>
+      <c r="D547" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="E547" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="F547" s="5">
+        <v>4</v>
+      </c>
+      <c r="G547" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="H547" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="I547" s="9">
+        <v>0.96</v>
+      </c>
+      <c r="J547" s="5">
+        <v>2</v>
+      </c>
+      <c r="K547" s="5">
+        <v>1</v>
+      </c>
+      <c r="L547" s="5">
         <v>1</v>
       </c>
     </row>
@@ -23769,8 +23809,10 @@
     <hyperlink ref="H545" r:id="rId1039" xr:uid="{66D5F5FA-0904-41C3-96F1-3185DF1AE153}"/>
     <hyperlink ref="E546" r:id="rId1040" xr:uid="{3DF07115-41AD-47DE-8A0A-6817CAD07E4F}"/>
     <hyperlink ref="H546" r:id="rId1041" xr:uid="{A3AC0014-61BD-4649-90B6-9AC2C895FEA4}"/>
+    <hyperlink ref="E547" r:id="rId1042" xr:uid="{A7302DAD-8723-42E6-9C50-C6DCA19CA1DF}"/>
+    <hyperlink ref="H547" r:id="rId1043" xr:uid="{64AB3C06-C80A-4238-B0B8-5B976204D4FE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1042"/>
+  <pageSetup orientation="portrait" r:id="rId1044"/>
 </worksheet>
 </file>
--- a/docs/CodeSignal/record.xlsx
+++ b/docs/CodeSignal/record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\everyday-use\Blog\docs\CodeSignal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D30805EA-2D64-4B5A-91B0-09574A7A9D88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F961F1F1-7858-4344-97B1-3D8EC4A4E99F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" tabRatio="511" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2196" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2200" uniqueCount="120">
   <si>
     <t>番号</t>
   </si>
@@ -947,7 +947,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:L547"/>
+  <dimension ref="A1:L548"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="7.7265625" style="10" bestFit="1" customWidth="1"/>
@@ -13446,7 +13446,7 @@
     </row>
     <row r="315" spans="1:12" ht="24" customHeight="1">
       <c r="A315" s="5">
-        <f t="shared" ref="A315:A547" si="8">ROW()-1</f>
+        <f t="shared" ref="A315:A548" si="8">ROW()-1</f>
         <v>314</v>
       </c>
       <c r="B315" s="6">
@@ -19330,7 +19330,7 @@
         <v>461</v>
       </c>
       <c r="B462" s="6">
-        <f t="shared" ref="B462:B547" si="10">B461+1</f>
+        <f t="shared" ref="B462:B548" si="10">B461+1</f>
         <v>46223</v>
       </c>
       <c r="C462" s="5">
@@ -22761,7 +22761,47 @@
         <v>1</v>
       </c>
       <c r="L547" s="5">
-        <v>1</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="548" spans="1:12" ht="24" customHeight="1">
+      <c r="A548" s="5">
+        <f t="shared" si="8"/>
+        <v>547</v>
+      </c>
+      <c r="B548" s="6">
+        <f t="shared" si="10"/>
+        <v>46309</v>
+      </c>
+      <c r="C548" s="5">
+        <v>833</v>
+      </c>
+      <c r="D548" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="E548" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="F548" s="5">
+        <v>4</v>
+      </c>
+      <c r="G548" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="H548" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="I548" s="9">
+        <v>0.96</v>
+      </c>
+      <c r="J548" s="5">
+        <v>2</v>
+      </c>
+      <c r="K548" s="5">
+        <v>1</v>
+      </c>
+      <c r="L548" s="5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -23811,8 +23851,10 @@
     <hyperlink ref="H546" r:id="rId1041" xr:uid="{A3AC0014-61BD-4649-90B6-9AC2C895FEA4}"/>
     <hyperlink ref="E547" r:id="rId1042" xr:uid="{A7302DAD-8723-42E6-9C50-C6DCA19CA1DF}"/>
     <hyperlink ref="H547" r:id="rId1043" xr:uid="{64AB3C06-C80A-4238-B0B8-5B976204D4FE}"/>
+    <hyperlink ref="E548" r:id="rId1044" xr:uid="{3B7A91D8-8992-417A-B935-4EFB1F0554DD}"/>
+    <hyperlink ref="H548" r:id="rId1045" xr:uid="{6D1435FA-63A2-4DBA-8858-2297C5362AE2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1044"/>
+  <pageSetup orientation="portrait" r:id="rId1046"/>
 </worksheet>
 </file>
--- a/docs/CodeSignal/record.xlsx
+++ b/docs/CodeSignal/record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\everyday-use\Blog\docs\CodeSignal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F961F1F1-7858-4344-97B1-3D8EC4A4E99F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36F10399-DB7B-4672-96DE-38EDBD68E03B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" tabRatio="511" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2200" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2204" uniqueCount="120">
   <si>
     <t>番号</t>
   </si>
@@ -947,7 +947,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:L548"/>
+  <dimension ref="A1:L549"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="7.7265625" style="10" bestFit="1" customWidth="1"/>
@@ -13446,7 +13446,7 @@
     </row>
     <row r="315" spans="1:12" ht="24" customHeight="1">
       <c r="A315" s="5">
-        <f t="shared" ref="A315:A548" si="8">ROW()-1</f>
+        <f t="shared" ref="A315:A549" si="8">ROW()-1</f>
         <v>314</v>
       </c>
       <c r="B315" s="6">
@@ -19330,7 +19330,7 @@
         <v>461</v>
       </c>
       <c r="B462" s="6">
-        <f t="shared" ref="B462:B548" si="10">B461+1</f>
+        <f t="shared" ref="B462:B549" si="10">B461+1</f>
         <v>46223</v>
       </c>
       <c r="C462" s="5">
@@ -22801,6 +22801,46 @@
         <v>1</v>
       </c>
       <c r="L548" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="549" spans="1:12" ht="24" customHeight="1">
+      <c r="A549" s="5">
+        <f t="shared" si="8"/>
+        <v>548</v>
+      </c>
+      <c r="B549" s="6">
+        <f t="shared" si="10"/>
+        <v>46310</v>
+      </c>
+      <c r="C549" s="5">
+        <v>833</v>
+      </c>
+      <c r="D549" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="E549" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="F549" s="5">
+        <v>4</v>
+      </c>
+      <c r="G549" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="H549" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="I549" s="9">
+        <v>0.96</v>
+      </c>
+      <c r="J549" s="5">
+        <v>2</v>
+      </c>
+      <c r="K549" s="5">
+        <v>1</v>
+      </c>
+      <c r="L549" s="5">
         <v>0</v>
       </c>
     </row>
@@ -23853,8 +23893,10 @@
     <hyperlink ref="H547" r:id="rId1043" xr:uid="{64AB3C06-C80A-4238-B0B8-5B976204D4FE}"/>
     <hyperlink ref="E548" r:id="rId1044" xr:uid="{3B7A91D8-8992-417A-B935-4EFB1F0554DD}"/>
     <hyperlink ref="H548" r:id="rId1045" xr:uid="{6D1435FA-63A2-4DBA-8858-2297C5362AE2}"/>
+    <hyperlink ref="E549" r:id="rId1046" xr:uid="{FBCDC7A6-957B-41E7-B6D9-229C16584653}"/>
+    <hyperlink ref="H549" r:id="rId1047" xr:uid="{12401DCE-6B31-42D3-ADD7-0B00A8D7ED6A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1046"/>
+  <pageSetup orientation="portrait" r:id="rId1048"/>
 </worksheet>
 </file>
--- a/docs/CodeSignal/record.xlsx
+++ b/docs/CodeSignal/record.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\everyday-use\Blog\docs\CodeSignal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36F10399-DB7B-4672-96DE-38EDBD68E03B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{767088CD-F83C-4904-9F92-A8F9BF78207A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" tabRatio="511" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19110" yWindow="0" windowWidth="19290" windowHeight="20880" tabRatio="511" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CodeSignalの記録" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2204" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2208" uniqueCount="120">
   <si>
     <t>番号</t>
   </si>
@@ -947,7 +947,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:L549"/>
+  <dimension ref="A1:L550"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="7.7265625" style="10" bestFit="1" customWidth="1"/>
@@ -13446,7 +13446,7 @@
     </row>
     <row r="315" spans="1:12" ht="24" customHeight="1">
       <c r="A315" s="5">
-        <f t="shared" ref="A315:A549" si="8">ROW()-1</f>
+        <f t="shared" ref="A315:A550" si="8">ROW()-1</f>
         <v>314</v>
       </c>
       <c r="B315" s="6">
@@ -19330,7 +19330,7 @@
         <v>461</v>
       </c>
       <c r="B462" s="6">
-        <f t="shared" ref="B462:B549" si="10">B461+1</f>
+        <f t="shared" ref="B462:B550" si="10">B461+1</f>
         <v>46223</v>
       </c>
       <c r="C462" s="5">
@@ -22758,7 +22758,7 @@
         <v>2</v>
       </c>
       <c r="K547" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L547" s="5">
         <v>0</v>
@@ -22798,7 +22798,7 @@
         <v>2</v>
       </c>
       <c r="K548" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L548" s="5">
         <v>0</v>
@@ -22838,10 +22838,50 @@
         <v>2</v>
       </c>
       <c r="K549" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L549" s="5">
         <v>0</v>
+      </c>
+    </row>
+    <row r="550" spans="1:12" ht="24" customHeight="1">
+      <c r="A550" s="5">
+        <f t="shared" si="8"/>
+        <v>549</v>
+      </c>
+      <c r="B550" s="6">
+        <f t="shared" si="10"/>
+        <v>46311</v>
+      </c>
+      <c r="C550" s="5">
+        <v>834</v>
+      </c>
+      <c r="D550" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="E550" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="F550" s="5">
+        <v>4</v>
+      </c>
+      <c r="G550" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="H550" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="I550" s="9">
+        <v>1</v>
+      </c>
+      <c r="J550" s="5">
+        <v>2</v>
+      </c>
+      <c r="K550" s="5">
+        <v>1</v>
+      </c>
+      <c r="L550" s="5">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -23895,8 +23935,10 @@
     <hyperlink ref="H548" r:id="rId1045" xr:uid="{6D1435FA-63A2-4DBA-8858-2297C5362AE2}"/>
     <hyperlink ref="E549" r:id="rId1046" xr:uid="{FBCDC7A6-957B-41E7-B6D9-229C16584653}"/>
     <hyperlink ref="H549" r:id="rId1047" xr:uid="{12401DCE-6B31-42D3-ADD7-0B00A8D7ED6A}"/>
+    <hyperlink ref="E550" r:id="rId1048" xr:uid="{613E0D07-9901-461B-8E0E-BBCFACD7330F}"/>
+    <hyperlink ref="H550" r:id="rId1049" xr:uid="{C14276A4-93B7-496A-888B-50FD19331DFF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1048"/>
+  <pageSetup orientation="portrait" r:id="rId1050"/>
 </worksheet>
 </file>
--- a/docs/CodeSignal/record.xlsx
+++ b/docs/CodeSignal/record.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\everyday-use\Blog\docs\CodeSignal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{767088CD-F83C-4904-9F92-A8F9BF78207A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E720466-F14B-4C38-8A3D-E85A29CBEC1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19110" yWindow="0" windowWidth="19290" windowHeight="20880" tabRatio="511" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" tabRatio="511" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CodeSignalの記録" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2208" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2212" uniqueCount="124">
   <si>
     <t>番号</t>
   </si>
@@ -501,6 +501,22 @@
     <t>https://codesignal.com/learn/courses/refactoring-by-leveraging-your-tests-with-typescript-jest</t>
     <phoneticPr fontId="4"/>
   </si>
+  <si>
+    <t>Foundations of Digital Logic &amp; Circuits</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://codesignal.com/learn/paths/foundations-of-digital-logic-circuits</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>Basic Logic Gates &amp; Fundamentals</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://codesignal.com/learn/courses/basic-logic-gates-fundamentals</t>
+    <phoneticPr fontId="4"/>
+  </si>
 </sst>
 </file>
 
@@ -947,7 +963,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:L550"/>
+  <dimension ref="A1:L551"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="7.7265625" style="10" bestFit="1" customWidth="1"/>
@@ -13446,7 +13462,7 @@
     </row>
     <row r="315" spans="1:12" ht="24" customHeight="1">
       <c r="A315" s="5">
-        <f t="shared" ref="A315:A550" si="8">ROW()-1</f>
+        <f t="shared" ref="A315:A551" si="8">ROW()-1</f>
         <v>314</v>
       </c>
       <c r="B315" s="6">
@@ -19330,7 +19346,7 @@
         <v>461</v>
       </c>
       <c r="B462" s="6">
-        <f t="shared" ref="B462:B550" si="10">B461+1</f>
+        <f t="shared" ref="B462:B551" si="10">B461+1</f>
         <v>46223</v>
       </c>
       <c r="C462" s="5">
@@ -22882,6 +22898,46 @@
       </c>
       <c r="L550" s="5">
         <v>1</v>
+      </c>
+    </row>
+    <row r="551" spans="1:12" ht="24" customHeight="1">
+      <c r="A551" s="5">
+        <f t="shared" si="8"/>
+        <v>550</v>
+      </c>
+      <c r="B551" s="6">
+        <f t="shared" si="10"/>
+        <v>46312</v>
+      </c>
+      <c r="C551" s="5">
+        <v>835</v>
+      </c>
+      <c r="D551" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="E551" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="F551" s="5">
+        <v>1</v>
+      </c>
+      <c r="G551" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="H551" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="I551" s="9">
+        <v>0.17</v>
+      </c>
+      <c r="J551" s="5">
+        <v>1</v>
+      </c>
+      <c r="K551" s="5">
+        <v>5</v>
+      </c>
+      <c r="L551" s="5">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -23937,8 +23993,10 @@
     <hyperlink ref="H549" r:id="rId1047" xr:uid="{12401DCE-6B31-42D3-ADD7-0B00A8D7ED6A}"/>
     <hyperlink ref="E550" r:id="rId1048" xr:uid="{613E0D07-9901-461B-8E0E-BBCFACD7330F}"/>
     <hyperlink ref="H550" r:id="rId1049" xr:uid="{C14276A4-93B7-496A-888B-50FD19331DFF}"/>
+    <hyperlink ref="E551" r:id="rId1050" xr:uid="{41AFDB05-8E32-41AE-BA33-DAE6B76F5271}"/>
+    <hyperlink ref="H551" r:id="rId1051" xr:uid="{A750DCBF-0FCC-4E40-950E-5E53E7F88E1B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1050"/>
+  <pageSetup orientation="portrait" r:id="rId1052"/>
 </worksheet>
 </file>
--- a/docs/CodeSignal/record.xlsx
+++ b/docs/CodeSignal/record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\everyday-use\Blog\docs\CodeSignal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E720466-F14B-4C38-8A3D-E85A29CBEC1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9F283B7-3CB2-494E-867C-4010283BE8F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" tabRatio="511" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2212" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2216" uniqueCount="124">
   <si>
     <t>番号</t>
   </si>
@@ -963,7 +963,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:L551"/>
+  <dimension ref="A1:L552"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="7.7265625" style="10" bestFit="1" customWidth="1"/>
@@ -13462,7 +13462,7 @@
     </row>
     <row r="315" spans="1:12" ht="24" customHeight="1">
       <c r="A315" s="5">
-        <f t="shared" ref="A315:A551" si="8">ROW()-1</f>
+        <f t="shared" ref="A315:A552" si="8">ROW()-1</f>
         <v>314</v>
       </c>
       <c r="B315" s="6">
@@ -19346,7 +19346,7 @@
         <v>461</v>
       </c>
       <c r="B462" s="6">
-        <f t="shared" ref="B462:B551" si="10">B461+1</f>
+        <f t="shared" ref="B462:B552" si="10">B461+1</f>
         <v>46223</v>
       </c>
       <c r="C462" s="5">
@@ -22938,6 +22938,46 @@
       </c>
       <c r="L551" s="5">
         <v>4</v>
+      </c>
+    </row>
+    <row r="552" spans="1:12" ht="24" customHeight="1">
+      <c r="A552" s="5">
+        <f t="shared" si="8"/>
+        <v>551</v>
+      </c>
+      <c r="B552" s="6">
+        <f t="shared" si="10"/>
+        <v>46313</v>
+      </c>
+      <c r="C552" s="5">
+        <v>836</v>
+      </c>
+      <c r="D552" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="E552" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="F552" s="5">
+        <v>1</v>
+      </c>
+      <c r="G552" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="H552" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="I552" s="9">
+        <v>0.34</v>
+      </c>
+      <c r="J552" s="5">
+        <v>2</v>
+      </c>
+      <c r="K552" s="5">
+        <v>5</v>
+      </c>
+      <c r="L552" s="5">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -23995,8 +24035,10 @@
     <hyperlink ref="H550" r:id="rId1049" xr:uid="{C14276A4-93B7-496A-888B-50FD19331DFF}"/>
     <hyperlink ref="E551" r:id="rId1050" xr:uid="{41AFDB05-8E32-41AE-BA33-DAE6B76F5271}"/>
     <hyperlink ref="H551" r:id="rId1051" xr:uid="{A750DCBF-0FCC-4E40-950E-5E53E7F88E1B}"/>
+    <hyperlink ref="E552" r:id="rId1052" xr:uid="{B17688C2-B776-4022-92A8-D4CEBB116DE4}"/>
+    <hyperlink ref="H552" r:id="rId1053" xr:uid="{70DD37BB-B1ED-4034-BE7D-74193F1A4A7D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1052"/>
+  <pageSetup orientation="portrait" r:id="rId1054"/>
 </worksheet>
 </file>
--- a/docs/CodeSignal/record.xlsx
+++ b/docs/CodeSignal/record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\everyday-use\Blog\docs\CodeSignal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9F283B7-3CB2-494E-867C-4010283BE8F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF74169F-257A-4FC9-BE59-9C868A385B7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" tabRatio="511" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2216" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2220" uniqueCount="124">
   <si>
     <t>番号</t>
   </si>
@@ -963,7 +963,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:L552"/>
+  <dimension ref="A1:L553"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="7.7265625" style="10" bestFit="1" customWidth="1"/>
@@ -13462,7 +13462,7 @@
     </row>
     <row r="315" spans="1:12" ht="24" customHeight="1">
       <c r="A315" s="5">
-        <f t="shared" ref="A315:A552" si="8">ROW()-1</f>
+        <f t="shared" ref="A315:A553" si="8">ROW()-1</f>
         <v>314</v>
       </c>
       <c r="B315" s="6">
@@ -19346,7 +19346,7 @@
         <v>461</v>
       </c>
       <c r="B462" s="6">
-        <f t="shared" ref="B462:B552" si="10">B461+1</f>
+        <f t="shared" ref="B462:B553" si="10">B461+1</f>
         <v>46223</v>
       </c>
       <c r="C462" s="5">
@@ -22978,6 +22978,46 @@
       </c>
       <c r="L552" s="5">
         <v>5</v>
+      </c>
+    </row>
+    <row r="553" spans="1:12" ht="24" customHeight="1">
+      <c r="A553" s="5">
+        <f t="shared" si="8"/>
+        <v>552</v>
+      </c>
+      <c r="B553" s="6">
+        <f t="shared" si="10"/>
+        <v>46314</v>
+      </c>
+      <c r="C553" s="5">
+        <v>837</v>
+      </c>
+      <c r="D553" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="E553" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="F553" s="5">
+        <v>1</v>
+      </c>
+      <c r="G553" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="H553" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="I553" s="9">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="J553" s="5">
+        <v>2</v>
+      </c>
+      <c r="K553" s="5">
+        <v>5</v>
+      </c>
+      <c r="L553" s="5">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -24037,8 +24077,10 @@
     <hyperlink ref="H551" r:id="rId1051" xr:uid="{A750DCBF-0FCC-4E40-950E-5E53E7F88E1B}"/>
     <hyperlink ref="E552" r:id="rId1052" xr:uid="{B17688C2-B776-4022-92A8-D4CEBB116DE4}"/>
     <hyperlink ref="H552" r:id="rId1053" xr:uid="{70DD37BB-B1ED-4034-BE7D-74193F1A4A7D}"/>
+    <hyperlink ref="E553" r:id="rId1054" xr:uid="{AE085452-0A62-442B-9B9B-B0A82E89D00B}"/>
+    <hyperlink ref="H553" r:id="rId1055" xr:uid="{1D8B5BB8-2BC0-4D87-A776-E7F1C5392455}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1054"/>
+  <pageSetup orientation="portrait" r:id="rId1056"/>
 </worksheet>
 </file>
--- a/docs/CodeSignal/record.xlsx
+++ b/docs/CodeSignal/record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\everyday-use\Blog\docs\CodeSignal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF74169F-257A-4FC9-BE59-9C868A385B7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{248ADEE9-1E51-4203-884E-6FF5E547648D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" tabRatio="511" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2220" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2224" uniqueCount="124">
   <si>
     <t>番号</t>
   </si>
@@ -963,7 +963,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:L553"/>
+  <dimension ref="A1:L554"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="7.7265625" style="10" bestFit="1" customWidth="1"/>
@@ -13462,7 +13462,7 @@
     </row>
     <row r="315" spans="1:12" ht="24" customHeight="1">
       <c r="A315" s="5">
-        <f t="shared" ref="A315:A553" si="8">ROW()-1</f>
+        <f t="shared" ref="A315:A554" si="8">ROW()-1</f>
         <v>314</v>
       </c>
       <c r="B315" s="6">
@@ -19346,7 +19346,7 @@
         <v>461</v>
       </c>
       <c r="B462" s="6">
-        <f t="shared" ref="B462:B553" si="10">B461+1</f>
+        <f t="shared" ref="B462:B554" si="10">B461+1</f>
         <v>46223</v>
       </c>
       <c r="C462" s="5">
@@ -23018,6 +23018,46 @@
       </c>
       <c r="L553" s="5">
         <v>4</v>
+      </c>
+    </row>
+    <row r="554" spans="1:12" ht="24" customHeight="1">
+      <c r="A554" s="5">
+        <f t="shared" si="8"/>
+        <v>553</v>
+      </c>
+      <c r="B554" s="6">
+        <f t="shared" si="10"/>
+        <v>46315</v>
+      </c>
+      <c r="C554" s="5">
+        <v>838</v>
+      </c>
+      <c r="D554" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="E554" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="F554" s="5">
+        <v>1</v>
+      </c>
+      <c r="G554" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="H554" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="I554" s="9">
+        <v>0.83</v>
+      </c>
+      <c r="J554" s="5">
+        <v>5</v>
+      </c>
+      <c r="K554" s="5">
+        <v>4</v>
+      </c>
+      <c r="L554" s="5">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -24079,8 +24119,10 @@
     <hyperlink ref="H552" r:id="rId1053" xr:uid="{70DD37BB-B1ED-4034-BE7D-74193F1A4A7D}"/>
     <hyperlink ref="E553" r:id="rId1054" xr:uid="{AE085452-0A62-442B-9B9B-B0A82E89D00B}"/>
     <hyperlink ref="H553" r:id="rId1055" xr:uid="{1D8B5BB8-2BC0-4D87-A776-E7F1C5392455}"/>
+    <hyperlink ref="E554" r:id="rId1056" xr:uid="{820E5AEF-41F7-46C1-BE67-DE4CC93DCA07}"/>
+    <hyperlink ref="H554" r:id="rId1057" xr:uid="{7CBF3C86-7010-463E-86EC-65BE67D877A7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1056"/>
+  <pageSetup orientation="portrait" r:id="rId1058"/>
 </worksheet>
 </file>
--- a/docs/CodeSignal/record.xlsx
+++ b/docs/CodeSignal/record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\everyday-use\Blog\docs\CodeSignal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{248ADEE9-1E51-4203-884E-6FF5E547648D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{891F8E25-85A0-46EA-AC84-C53F36CCB419}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" tabRatio="511" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2224" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2228" uniqueCount="124">
   <si>
     <t>番号</t>
   </si>
@@ -963,7 +963,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:L554"/>
+  <dimension ref="A1:L555"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="7.7265625" style="10" bestFit="1" customWidth="1"/>
@@ -13462,7 +13462,7 @@
     </row>
     <row r="315" spans="1:12" ht="24" customHeight="1">
       <c r="A315" s="5">
-        <f t="shared" ref="A315:A554" si="8">ROW()-1</f>
+        <f t="shared" ref="A315:A555" si="8">ROW()-1</f>
         <v>314</v>
       </c>
       <c r="B315" s="6">
@@ -19346,7 +19346,7 @@
         <v>461</v>
       </c>
       <c r="B462" s="6">
-        <f t="shared" ref="B462:B554" si="10">B461+1</f>
+        <f t="shared" ref="B462:B555" si="10">B461+1</f>
         <v>46223</v>
       </c>
       <c r="C462" s="5">
@@ -23058,6 +23058,46 @@
       </c>
       <c r="L554" s="5">
         <v>3</v>
+      </c>
+    </row>
+    <row r="555" spans="1:12" ht="24" customHeight="1">
+      <c r="A555" s="5">
+        <f t="shared" si="8"/>
+        <v>554</v>
+      </c>
+      <c r="B555" s="6">
+        <f t="shared" si="10"/>
+        <v>46316</v>
+      </c>
+      <c r="C555" s="5">
+        <v>839</v>
+      </c>
+      <c r="D555" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="E555" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="F555" s="5">
+        <v>1</v>
+      </c>
+      <c r="G555" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="H555" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="I555" s="9">
+        <v>0.87</v>
+      </c>
+      <c r="J555" s="5">
+        <v>5</v>
+      </c>
+      <c r="K555" s="5">
+        <v>1</v>
+      </c>
+      <c r="L555" s="5">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -24121,8 +24161,10 @@
     <hyperlink ref="H553" r:id="rId1055" xr:uid="{1D8B5BB8-2BC0-4D87-A776-E7F1C5392455}"/>
     <hyperlink ref="E554" r:id="rId1056" xr:uid="{820E5AEF-41F7-46C1-BE67-DE4CC93DCA07}"/>
     <hyperlink ref="H554" r:id="rId1057" xr:uid="{7CBF3C86-7010-463E-86EC-65BE67D877A7}"/>
+    <hyperlink ref="E555" r:id="rId1058" xr:uid="{14E52687-95B6-4DFA-BC78-B5669DE7A64E}"/>
+    <hyperlink ref="H555" r:id="rId1059" xr:uid="{E0A3BD7E-D505-4FEA-8BC3-B8405D7EA870}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1058"/>
+  <pageSetup orientation="portrait" r:id="rId1060"/>
 </worksheet>
 </file>
--- a/docs/CodeSignal/record.xlsx
+++ b/docs/CodeSignal/record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\everyday-use\Blog\docs\CodeSignal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{891F8E25-85A0-46EA-AC84-C53F36CCB419}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E43A8DEC-CCA9-4506-9FB9-829C056B62BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" tabRatio="511" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2228" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2232" uniqueCount="124">
   <si>
     <t>番号</t>
   </si>
@@ -963,7 +963,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:L555"/>
+  <dimension ref="A1:L556"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="7.7265625" style="10" bestFit="1" customWidth="1"/>
@@ -13462,7 +13462,7 @@
     </row>
     <row r="315" spans="1:12" ht="24" customHeight="1">
       <c r="A315" s="5">
-        <f t="shared" ref="A315:A555" si="8">ROW()-1</f>
+        <f t="shared" ref="A315:A556" si="8">ROW()-1</f>
         <v>314</v>
       </c>
       <c r="B315" s="6">
@@ -19346,7 +19346,7 @@
         <v>461</v>
       </c>
       <c r="B462" s="6">
-        <f t="shared" ref="B462:B555" si="10">B461+1</f>
+        <f t="shared" ref="B462:B556" si="10">B461+1</f>
         <v>46223</v>
       </c>
       <c r="C462" s="5">
@@ -23098,6 +23098,46 @@
       </c>
       <c r="L555" s="5">
         <v>1</v>
+      </c>
+    </row>
+    <row r="556" spans="1:12" ht="24" customHeight="1">
+      <c r="A556" s="5">
+        <f t="shared" si="8"/>
+        <v>555</v>
+      </c>
+      <c r="B556" s="6">
+        <f t="shared" si="10"/>
+        <v>46317</v>
+      </c>
+      <c r="C556" s="5">
+        <v>840</v>
+      </c>
+      <c r="D556" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="E556" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="F556" s="5">
+        <v>1</v>
+      </c>
+      <c r="G556" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="H556" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="I556" s="9">
+        <v>0.97</v>
+      </c>
+      <c r="J556" s="5">
+        <v>5</v>
+      </c>
+      <c r="K556" s="5">
+        <v>4</v>
+      </c>
+      <c r="L556" s="5">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -24163,8 +24203,10 @@
     <hyperlink ref="H554" r:id="rId1057" xr:uid="{7CBF3C86-7010-463E-86EC-65BE67D877A7}"/>
     <hyperlink ref="E555" r:id="rId1058" xr:uid="{14E52687-95B6-4DFA-BC78-B5669DE7A64E}"/>
     <hyperlink ref="H555" r:id="rId1059" xr:uid="{E0A3BD7E-D505-4FEA-8BC3-B8405D7EA870}"/>
+    <hyperlink ref="E556" r:id="rId1060" xr:uid="{B07A2523-58A2-4E8D-A180-93A23B6FCBF5}"/>
+    <hyperlink ref="H556" r:id="rId1061" xr:uid="{9486364F-7B5B-4810-ACC5-5F3E3FD309D4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1060"/>
+  <pageSetup orientation="portrait" r:id="rId1062"/>
 </worksheet>
 </file>
--- a/docs/CodeSignal/record.xlsx
+++ b/docs/CodeSignal/record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\everyday-use\Blog\docs\CodeSignal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E43A8DEC-CCA9-4506-9FB9-829C056B62BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F610181-707A-4798-8742-999697080635}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" tabRatio="511" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2232" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2240" uniqueCount="124">
   <si>
     <t>番号</t>
   </si>
@@ -963,7 +963,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:L556"/>
+  <dimension ref="A1:L558"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="7.7265625" style="10" bestFit="1" customWidth="1"/>
@@ -13462,7 +13462,7 @@
     </row>
     <row r="315" spans="1:12" ht="24" customHeight="1">
       <c r="A315" s="5">
-        <f t="shared" ref="A315:A556" si="8">ROW()-1</f>
+        <f t="shared" ref="A315:A558" si="8">ROW()-1</f>
         <v>314</v>
       </c>
       <c r="B315" s="6">
@@ -19346,7 +19346,7 @@
         <v>461</v>
       </c>
       <c r="B462" s="6">
-        <f t="shared" ref="B462:B556" si="10">B461+1</f>
+        <f t="shared" ref="B462:B558" si="10">B461+1</f>
         <v>46223</v>
       </c>
       <c r="C462" s="5">
@@ -23138,6 +23138,86 @@
       </c>
       <c r="L556" s="5">
         <v>3</v>
+      </c>
+    </row>
+    <row r="557" spans="1:12" ht="24" customHeight="1">
+      <c r="A557" s="5">
+        <f t="shared" si="8"/>
+        <v>556</v>
+      </c>
+      <c r="B557" s="6">
+        <f t="shared" si="10"/>
+        <v>46318</v>
+      </c>
+      <c r="C557" s="5">
+        <v>840</v>
+      </c>
+      <c r="D557" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="E557" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="F557" s="5">
+        <v>1</v>
+      </c>
+      <c r="G557" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="H557" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="I557" s="9">
+        <v>0.97</v>
+      </c>
+      <c r="J557" s="5">
+        <v>5</v>
+      </c>
+      <c r="K557" s="5">
+        <v>0</v>
+      </c>
+      <c r="L557" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="558" spans="1:12" ht="24" customHeight="1">
+      <c r="A558" s="5">
+        <f t="shared" si="8"/>
+        <v>557</v>
+      </c>
+      <c r="B558" s="6">
+        <f t="shared" si="10"/>
+        <v>46319</v>
+      </c>
+      <c r="C558" s="5">
+        <v>840</v>
+      </c>
+      <c r="D558" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="E558" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="F558" s="5">
+        <v>1</v>
+      </c>
+      <c r="G558" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="H558" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="I558" s="9">
+        <v>0.97</v>
+      </c>
+      <c r="J558" s="5">
+        <v>5</v>
+      </c>
+      <c r="K558" s="5">
+        <v>0</v>
+      </c>
+      <c r="L558" s="5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -24205,8 +24285,12 @@
     <hyperlink ref="H555" r:id="rId1059" xr:uid="{E0A3BD7E-D505-4FEA-8BC3-B8405D7EA870}"/>
     <hyperlink ref="E556" r:id="rId1060" xr:uid="{B07A2523-58A2-4E8D-A180-93A23B6FCBF5}"/>
     <hyperlink ref="H556" r:id="rId1061" xr:uid="{9486364F-7B5B-4810-ACC5-5F3E3FD309D4}"/>
+    <hyperlink ref="E557" r:id="rId1062" xr:uid="{CA8D6482-37BB-4FFD-BFFE-111002759A90}"/>
+    <hyperlink ref="H557" r:id="rId1063" xr:uid="{1D5741C6-3EBE-492D-BBD0-6BA561BA18C2}"/>
+    <hyperlink ref="E558" r:id="rId1064" xr:uid="{AE0F004F-4ECF-451E-8BFC-56DF14D4E2E8}"/>
+    <hyperlink ref="H558" r:id="rId1065" xr:uid="{E1320B3F-B58B-4549-BA3B-B51BA58DC5BE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1062"/>
+  <pageSetup orientation="portrait" r:id="rId1066"/>
 </worksheet>
 </file>
--- a/docs/CodeSignal/record.xlsx
+++ b/docs/CodeSignal/record.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\everyday-use\Blog\docs\CodeSignal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F610181-707A-4798-8742-999697080635}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E11D6F60-3AD6-47B8-8387-AC579987A674}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" tabRatio="511" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="511" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CodeSignalの記録" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2240" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2244" uniqueCount="124">
   <si>
     <t>番号</t>
   </si>
@@ -963,7 +963,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:L558"/>
+  <dimension ref="A1:L559"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="7.7265625" style="10" bestFit="1" customWidth="1"/>
@@ -13462,7 +13462,7 @@
     </row>
     <row r="315" spans="1:12" ht="24" customHeight="1">
       <c r="A315" s="5">
-        <f t="shared" ref="A315:A558" si="8">ROW()-1</f>
+        <f t="shared" ref="A315:A559" si="8">ROW()-1</f>
         <v>314</v>
       </c>
       <c r="B315" s="6">
@@ -19346,7 +19346,7 @@
         <v>461</v>
       </c>
       <c r="B462" s="6">
-        <f t="shared" ref="B462:B558" si="10">B461+1</f>
+        <f t="shared" ref="B462:B559" si="10">B461+1</f>
         <v>46223</v>
       </c>
       <c r="C462" s="5">
@@ -23217,6 +23217,46 @@
         <v>0</v>
       </c>
       <c r="L558" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="559" spans="1:12" ht="24" customHeight="1">
+      <c r="A559" s="5">
+        <f t="shared" si="8"/>
+        <v>558</v>
+      </c>
+      <c r="B559" s="6">
+        <f t="shared" si="10"/>
+        <v>46320</v>
+      </c>
+      <c r="C559" s="5">
+        <v>840</v>
+      </c>
+      <c r="D559" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="E559" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="F559" s="5">
+        <v>1</v>
+      </c>
+      <c r="G559" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="H559" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="I559" s="9">
+        <v>0.97</v>
+      </c>
+      <c r="J559" s="5">
+        <v>5</v>
+      </c>
+      <c r="K559" s="5">
+        <v>0</v>
+      </c>
+      <c r="L559" s="5">
         <v>0</v>
       </c>
     </row>
@@ -24289,8 +24329,10 @@
     <hyperlink ref="H557" r:id="rId1063" xr:uid="{1D5741C6-3EBE-492D-BBD0-6BA561BA18C2}"/>
     <hyperlink ref="E558" r:id="rId1064" xr:uid="{AE0F004F-4ECF-451E-8BFC-56DF14D4E2E8}"/>
     <hyperlink ref="H558" r:id="rId1065" xr:uid="{E1320B3F-B58B-4549-BA3B-B51BA58DC5BE}"/>
+    <hyperlink ref="E559" r:id="rId1066" xr:uid="{1378E629-AAF3-40A8-B124-8AF8FE821CF3}"/>
+    <hyperlink ref="H559" r:id="rId1067" xr:uid="{2D7FB425-C60F-447A-9436-9BA01D2E26EF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1066"/>
+  <pageSetup orientation="portrait" r:id="rId1068"/>
 </worksheet>
 </file>
--- a/docs/CodeSignal/record.xlsx
+++ b/docs/CodeSignal/record.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\everyday-use\Blog\docs\CodeSignal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E11D6F60-3AD6-47B8-8387-AC579987A674}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE877FAF-10E6-417A-883B-11A3291FD021}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="511" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" tabRatio="511" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CodeSignalの記録" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2244" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2252" uniqueCount="124">
   <si>
     <t>番号</t>
   </si>
@@ -963,7 +963,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:L559"/>
+  <dimension ref="A1:L561"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="7.7265625" style="10" bestFit="1" customWidth="1"/>
@@ -13462,7 +13462,7 @@
     </row>
     <row r="315" spans="1:12" ht="24" customHeight="1">
       <c r="A315" s="5">
-        <f t="shared" ref="A315:A559" si="8">ROW()-1</f>
+        <f t="shared" ref="A315:A561" si="8">ROW()-1</f>
         <v>314</v>
       </c>
       <c r="B315" s="6">
@@ -19346,7 +19346,7 @@
         <v>461</v>
       </c>
       <c r="B462" s="6">
-        <f t="shared" ref="B462:B559" si="10">B461+1</f>
+        <f t="shared" ref="B462:B561" si="10">B461+1</f>
         <v>46223</v>
       </c>
       <c r="C462" s="5">
@@ -23257,6 +23257,86 @@
         <v>0</v>
       </c>
       <c r="L559" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="560" spans="1:12" ht="24" customHeight="1">
+      <c r="A560" s="5">
+        <f t="shared" si="8"/>
+        <v>559</v>
+      </c>
+      <c r="B560" s="6">
+        <f t="shared" si="10"/>
+        <v>46321</v>
+      </c>
+      <c r="C560" s="5">
+        <v>841</v>
+      </c>
+      <c r="D560" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="E560" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="F560" s="5">
+        <v>1</v>
+      </c>
+      <c r="G560" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="H560" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="I560" s="9">
+        <v>1</v>
+      </c>
+      <c r="J560" s="5">
+        <v>100</v>
+      </c>
+      <c r="K560" s="5">
+        <v>1</v>
+      </c>
+      <c r="L560" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="561" spans="1:12" ht="24" customHeight="1">
+      <c r="A561" s="5">
+        <f t="shared" si="8"/>
+        <v>560</v>
+      </c>
+      <c r="B561" s="6">
+        <f t="shared" si="10"/>
+        <v>46322</v>
+      </c>
+      <c r="C561" s="5">
+        <v>841</v>
+      </c>
+      <c r="D561" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="E561" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="F561" s="5">
+        <v>1</v>
+      </c>
+      <c r="G561" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="H561" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="I561" s="9">
+        <v>1</v>
+      </c>
+      <c r="J561" s="5">
+        <v>100</v>
+      </c>
+      <c r="K561" s="5">
+        <v>0</v>
+      </c>
+      <c r="L561" s="5">
         <v>0</v>
       </c>
     </row>
@@ -24331,8 +24411,12 @@
     <hyperlink ref="H558" r:id="rId1065" xr:uid="{E1320B3F-B58B-4549-BA3B-B51BA58DC5BE}"/>
     <hyperlink ref="E559" r:id="rId1066" xr:uid="{1378E629-AAF3-40A8-B124-8AF8FE821CF3}"/>
     <hyperlink ref="H559" r:id="rId1067" xr:uid="{2D7FB425-C60F-447A-9436-9BA01D2E26EF}"/>
+    <hyperlink ref="E560" r:id="rId1068" xr:uid="{78B3F642-B9EF-4E86-9710-AF3E68138771}"/>
+    <hyperlink ref="H560" r:id="rId1069" xr:uid="{F89B7641-0A9B-4325-9BA7-ABF19699671E}"/>
+    <hyperlink ref="E561" r:id="rId1070" xr:uid="{B24D9CFD-3B02-44E5-962C-6F36587985F5}"/>
+    <hyperlink ref="H561" r:id="rId1071" xr:uid="{E66716FB-04B6-4E87-A375-5E4D67942E8C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1068"/>
+  <pageSetup orientation="portrait" r:id="rId1072"/>
 </worksheet>
 </file>
--- a/docs/CodeSignal/record.xlsx
+++ b/docs/CodeSignal/record.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\everyday-use\Blog\docs\CodeSignal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE877FAF-10E6-417A-883B-11A3291FD021}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34155F33-0969-4D69-91AD-93604E961CA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" tabRatio="511" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="511" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CodeSignalの記録" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2252" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2256" uniqueCount="124">
   <si>
     <t>番号</t>
   </si>
@@ -963,7 +963,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:L561"/>
+  <dimension ref="A1:L562"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="7.7265625" style="10" bestFit="1" customWidth="1"/>
@@ -13462,7 +13462,7 @@
     </row>
     <row r="315" spans="1:12" ht="24" customHeight="1">
       <c r="A315" s="5">
-        <f t="shared" ref="A315:A561" si="8">ROW()-1</f>
+        <f t="shared" ref="A315:A562" si="8">ROW()-1</f>
         <v>314</v>
       </c>
       <c r="B315" s="6">
@@ -19346,7 +19346,7 @@
         <v>461</v>
       </c>
       <c r="B462" s="6">
-        <f t="shared" ref="B462:B561" si="10">B461+1</f>
+        <f t="shared" ref="B462:B562" si="10">B461+1</f>
         <v>46223</v>
       </c>
       <c r="C462" s="5">
@@ -23337,6 +23337,46 @@
         <v>0</v>
       </c>
       <c r="L561" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="562" spans="1:12" ht="24" customHeight="1">
+      <c r="A562" s="5">
+        <f t="shared" si="8"/>
+        <v>561</v>
+      </c>
+      <c r="B562" s="6">
+        <f t="shared" si="10"/>
+        <v>46323</v>
+      </c>
+      <c r="C562" s="5">
+        <v>841</v>
+      </c>
+      <c r="D562" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="E562" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="F562" s="5">
+        <v>1</v>
+      </c>
+      <c r="G562" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="H562" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="I562" s="9">
+        <v>1</v>
+      </c>
+      <c r="J562" s="5">
+        <v>100</v>
+      </c>
+      <c r="K562" s="5">
+        <v>0</v>
+      </c>
+      <c r="L562" s="5">
         <v>0</v>
       </c>
     </row>
@@ -24415,8 +24455,10 @@
     <hyperlink ref="H560" r:id="rId1069" xr:uid="{F89B7641-0A9B-4325-9BA7-ABF19699671E}"/>
     <hyperlink ref="E561" r:id="rId1070" xr:uid="{B24D9CFD-3B02-44E5-962C-6F36587985F5}"/>
     <hyperlink ref="H561" r:id="rId1071" xr:uid="{E66716FB-04B6-4E87-A375-5E4D67942E8C}"/>
+    <hyperlink ref="E562" r:id="rId1072" xr:uid="{AB0CA6B3-3CB6-4516-B125-96B1CF6A85C2}"/>
+    <hyperlink ref="H562" r:id="rId1073" xr:uid="{408B1A31-A197-4918-9E77-DBFB16CE0CE8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1072"/>
+  <pageSetup orientation="portrait" r:id="rId1074"/>
 </worksheet>
 </file>
--- a/docs/CodeSignal/record.xlsx
+++ b/docs/CodeSignal/record.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\everyday-use\Blog\docs\CodeSignal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34155F33-0969-4D69-91AD-93604E961CA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{234F6E30-34E0-44F8-821F-A9503663CA77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="511" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" tabRatio="511" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CodeSignalの記録" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2256" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2260" uniqueCount="126">
   <si>
     <t>番号</t>
   </si>
@@ -517,6 +517,14 @@
     <t>https://codesignal.com/learn/courses/basic-logic-gates-fundamentals</t>
     <phoneticPr fontId="4"/>
   </si>
+  <si>
+    <t>Combining Gates to Build Meaning</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>https://github.com/KenichiroArai/everyday-use-git/issues/384</t>
+    <phoneticPr fontId="4"/>
+  </si>
 </sst>
 </file>
 
@@ -963,7 +971,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:L562"/>
+  <dimension ref="A1:L563"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="7.7265625" style="10" bestFit="1" customWidth="1"/>
@@ -13462,7 +13470,7 @@
     </row>
     <row r="315" spans="1:12" ht="24" customHeight="1">
       <c r="A315" s="5">
-        <f t="shared" ref="A315:A562" si="8">ROW()-1</f>
+        <f t="shared" ref="A315:A563" si="8">ROW()-1</f>
         <v>314</v>
       </c>
       <c r="B315" s="6">
@@ -19346,7 +19354,7 @@
         <v>461</v>
       </c>
       <c r="B462" s="6">
-        <f t="shared" ref="B462:B562" si="10">B461+1</f>
+        <f t="shared" ref="B462:B563" si="10">B461+1</f>
         <v>46223</v>
       </c>
       <c r="C462" s="5">
@@ -23291,7 +23299,7 @@
         <v>1</v>
       </c>
       <c r="J560" s="5">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="K560" s="5">
         <v>1</v>
@@ -23331,7 +23339,7 @@
         <v>1</v>
       </c>
       <c r="J561" s="5">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="K561" s="5">
         <v>0</v>
@@ -23371,12 +23379,52 @@
         <v>1</v>
       </c>
       <c r="J562" s="5">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="K562" s="5">
         <v>0</v>
       </c>
       <c r="L562" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="563" spans="1:12" ht="24" customHeight="1">
+      <c r="A563" s="5">
+        <f t="shared" si="8"/>
+        <v>562</v>
+      </c>
+      <c r="B563" s="6">
+        <f t="shared" si="10"/>
+        <v>46324</v>
+      </c>
+      <c r="C563" s="5">
+        <v>1</v>
+      </c>
+      <c r="D563" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="E563" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="F563" s="5">
+        <v>2</v>
+      </c>
+      <c r="G563" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="H563" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="I563" s="9">
+        <v>0.03</v>
+      </c>
+      <c r="J563" s="5">
+        <v>1</v>
+      </c>
+      <c r="K563" s="5">
+        <v>0</v>
+      </c>
+      <c r="L563" s="5">
         <v>0</v>
       </c>
     </row>
@@ -24457,8 +24505,10 @@
     <hyperlink ref="H561" r:id="rId1071" xr:uid="{E66716FB-04B6-4E87-A375-5E4D67942E8C}"/>
     <hyperlink ref="E562" r:id="rId1072" xr:uid="{AB0CA6B3-3CB6-4516-B125-96B1CF6A85C2}"/>
     <hyperlink ref="H562" r:id="rId1073" xr:uid="{408B1A31-A197-4918-9E77-DBFB16CE0CE8}"/>
+    <hyperlink ref="E563" r:id="rId1074" xr:uid="{B59CC2C7-D5B7-4981-9690-7AA8FE602416}"/>
+    <hyperlink ref="H563" r:id="rId1075" xr:uid="{82EB77C1-1589-45DE-96B6-96D8455ED817}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1074"/>
+  <pageSetup orientation="portrait" r:id="rId1076"/>
 </worksheet>
 </file>
--- a/docs/CodeSignal/record.xlsx
+++ b/docs/CodeSignal/record.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\everyday-use\Blog\docs\CodeSignal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{234F6E30-34E0-44F8-821F-A9503663CA77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9223355D-7B21-4385-9D99-21D0BB892215}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" tabRatio="511" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19020" yWindow="0" windowWidth="19380" windowHeight="20970" tabRatio="511" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CodeSignalの記録" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2260" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2264" uniqueCount="126">
   <si>
     <t>番号</t>
   </si>
@@ -971,7 +971,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:L563"/>
+  <dimension ref="A1:L564"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="7.7265625" style="10" bestFit="1" customWidth="1"/>
@@ -13470,7 +13470,7 @@
     </row>
     <row r="315" spans="1:12" ht="24" customHeight="1">
       <c r="A315" s="5">
-        <f t="shared" ref="A315:A563" si="8">ROW()-1</f>
+        <f t="shared" ref="A315:A564" si="8">ROW()-1</f>
         <v>314</v>
       </c>
       <c r="B315" s="6">
@@ -19354,7 +19354,7 @@
         <v>461</v>
       </c>
       <c r="B462" s="6">
-        <f t="shared" ref="B462:B563" si="10">B461+1</f>
+        <f t="shared" ref="B462:B564" si="10">B461+1</f>
         <v>46223</v>
       </c>
       <c r="C462" s="5">
@@ -23425,6 +23425,46 @@
         <v>0</v>
       </c>
       <c r="L563" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="564" spans="1:12" ht="24" customHeight="1">
+      <c r="A564" s="5">
+        <f t="shared" si="8"/>
+        <v>563</v>
+      </c>
+      <c r="B564" s="6">
+        <f t="shared" si="10"/>
+        <v>46325</v>
+      </c>
+      <c r="C564" s="5">
+        <v>1</v>
+      </c>
+      <c r="D564" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="E564" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="F564" s="5">
+        <v>2</v>
+      </c>
+      <c r="G564" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="H564" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="I564" s="9">
+        <v>0.03</v>
+      </c>
+      <c r="J564" s="5">
+        <v>1</v>
+      </c>
+      <c r="K564" s="5">
+        <v>0</v>
+      </c>
+      <c r="L564" s="5">
         <v>0</v>
       </c>
     </row>
@@ -24507,8 +24547,10 @@
     <hyperlink ref="H562" r:id="rId1073" xr:uid="{408B1A31-A197-4918-9E77-DBFB16CE0CE8}"/>
     <hyperlink ref="E563" r:id="rId1074" xr:uid="{B59CC2C7-D5B7-4981-9690-7AA8FE602416}"/>
     <hyperlink ref="H563" r:id="rId1075" xr:uid="{82EB77C1-1589-45DE-96B6-96D8455ED817}"/>
+    <hyperlink ref="E564" r:id="rId1076" xr:uid="{448E3967-E0E9-4FB9-A0E7-D76BA544C99A}"/>
+    <hyperlink ref="H564" r:id="rId1077" xr:uid="{047DFE00-A64A-4790-8AD9-A387529C4928}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1076"/>
+  <pageSetup orientation="portrait" r:id="rId1078"/>
 </worksheet>
 </file>
--- a/docs/CodeSignal/record.xlsx
+++ b/docs/CodeSignal/record.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\everyday-use-wk\everyday-use\Blog\docs\CodeSignal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9223355D-7B21-4385-9D99-21D0BB892215}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F6FD9BB-37F5-41D2-B94A-D397DAFC55AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19020" yWindow="0" windowWidth="19380" windowHeight="20970" tabRatio="511" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="511" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CodeSignalの記録" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2264" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2268" uniqueCount="126">
   <si>
     <t>番号</t>
   </si>
@@ -971,7 +971,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:L564"/>
+  <dimension ref="A1:L565"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="7.7265625" style="10" bestFit="1" customWidth="1"/>
@@ -13470,7 +13470,7 @@
     </row>
     <row r="315" spans="1:12" ht="24" customHeight="1">
       <c r="A315" s="5">
-        <f t="shared" ref="A315:A564" si="8">ROW()-1</f>
+        <f t="shared" ref="A315:A565" si="8">ROW()-1</f>
         <v>314</v>
       </c>
       <c r="B315" s="6">
@@ -19354,7 +19354,7 @@
         <v>461</v>
       </c>
       <c r="B462" s="6">
-        <f t="shared" ref="B462:B564" si="10">B461+1</f>
+        <f t="shared" ref="B462:B565" si="10">B461+1</f>
         <v>46223</v>
       </c>
       <c r="C462" s="5">
@@ -23465,6 +23465,46 @@
         <v>0</v>
       </c>
       <c r="L564" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="565" spans="1:12" ht="24" customHeight="1">
+      <c r="A565" s="5">
+        <f t="shared" si="8"/>
+        <v>564</v>
+      </c>
+      <c r="B565" s="6">
+        <f t="shared" si="10"/>
+        <v>46326</v>
+      </c>
+      <c r="C565" s="5">
+        <v>1</v>
+      </c>
+      <c r="D565" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="E565" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="F565" s="5">
+        <v>2</v>
+      </c>
+      <c r="G565" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="H565" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="I565" s="9">
+        <v>0.03</v>
+      </c>
+      <c r="J565" s="5">
+        <v>1</v>
+      </c>
+      <c r="K565" s="5">
+        <v>0</v>
+      </c>
+      <c r="L565" s="5">
         <v>0</v>
       </c>
     </row>
@@ -24549,8 +24589,10 @@
     <hyperlink ref="H563" r:id="rId1075" xr:uid="{82EB77C1-1589-45DE-96B6-96D8455ED817}"/>
     <hyperlink ref="E564" r:id="rId1076" xr:uid="{448E3967-E0E9-4FB9-A0E7-D76BA544C99A}"/>
     <hyperlink ref="H564" r:id="rId1077" xr:uid="{047DFE00-A64A-4790-8AD9-A387529C4928}"/>
+    <hyperlink ref="E565" r:id="rId1078" xr:uid="{BC344F61-17A1-4DC8-A6A0-BBDB0424DB02}"/>
+    <hyperlink ref="H565" r:id="rId1079" xr:uid="{F03E09D4-897B-43A5-9FFC-219E866A64E3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1078"/>
+  <pageSetup orientation="portrait" r:id="rId1080"/>
 </worksheet>
 </file>